--- a/content/Question Bank/Coding Questions/Unit 9 - Basic Object-Oriented Programming/Unit 9 - Basic Object-Oriented Programming - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 9 - Basic Object-Oriented Programming/Unit 9 - Basic Object-Oriented Programming - Coding Questions.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Define a Rectangle class with a width and a height and a method that returns its area. Read a width and height, create a Rectangle, and print its area.
+          <t>Sneha is putting up a poster for the college fest and needs to know how much space it will cover on the notice board so she can buy the right amount of chart paper. Define a `Rectangle` class that stores a width and a height and has a method that returns its area (width times height). Read a width and a height from input, create a `Rectangle` object, and print its area.
 ### Input Format
 - Line 1: Width
 - Line 2: Height
@@ -604,6 +604,8 @@
 ```
 12
 ```
+### Example Walkthrough
+For the sample input, the width is 3 and the height is 4. The `Rectangle` object stores these values, and its area method returns 3 x 4 = 12, so the program prints `12`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -755,14 +757,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Define a Point class that stores x and y coordinates. Read x and y, create a Point, and print it in the form (x, y).
+          <t>For the campus treasure hunt, every clue location is marked as a point on a grid map of the college. The organisers need a neat way to store and display each location. Define a `Point` class that stores `x` and `y` coordinates. Read `x` and `y` from input, create a `Point` object, and print it in the form `(x, y)`.
 ### Input Format
-- Line 1: x
-- Line 2: y
+- Line 1: `x`
+- Line 2: `y`
 ### Output Format
 ```
 (3, 4)
 ```
+### Example Walkthrough
+For the sample input, `x` is 3 and `y` is 4. The `Point` object stores both coordinates, and printing it in the required form gives `(3, 4)`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -913,13 +917,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Define a Student class that stores a name and has a method greet() returning 'Hi, I am &lt;name&gt;'. Read a name and print the greeting.
+          <t>On the first day of the semester, every student in the Python lab introduces themselves with a short greeting shown on the projector. Define a `Student` class that stores a name and has a method `greet()` that returns `Hi, I am &lt;name&gt;`. Read a name from input, create a `Student` object, and print the greeting.
 ### Input Format
 - Line 1: A name
 ### Output Format
 ```
 Hi, I am Asha
 ```
+### Example Walkthrough
+For the sample input, the name is `Asha`. The `Student` object stores this name, and `greet()` returns `Hi, I am Asha`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1061,7 +1067,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Define a Car class that stores a brand and a year and has a method describe() returning '&lt;year&gt; &lt;brand&gt;'. Read a brand and a year and print the description.
+          <t>Rohan is listing his family's old car on a second-hand vehicle website, and every listing shows the year followed by the brand. Define a `Car` class that stores a brand and a year and has a method `describe()` that returns `&lt;year&gt; &lt;brand&gt;`. Read a brand and a year from input, create a `Car` object, and print the description.
 ### Input Format
 - Line 1: Brand
 - Line 2: Year
@@ -1069,6 +1075,8 @@
 ```
 2020 Toyota
 ```
+### Example Walkthrough
+For the sample input, the brand is `Toyota` and the year is 2020. The `Car` object stores both, and `describe()` returns `2020 Toyota`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1220,15 +1228,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Define a BankAccount class with deposit and withdraw methods; a withdraw that exceeds the balance is ignored. Read a starting balance, then N operations like 'deposit 50' or 'withdraw 30', and print the final balance.
+          <t>Students in Anish's hostel use a prepaid mess card: they top it up with money and pay for meals from it, but the card simply refuses any payment larger than the balance. Define a `BankAccount` class with `deposit` and `withdraw` methods, where a `withdraw` that exceeds the balance is ignored. Read a starting balance, then `N` operations like `deposit 50` or `withdraw 30`, apply them in order, and print the final balance.
 ### Input Format
 - Line 1: Starting balance
-- Line 2: N
-- Next N lines: 'deposit X' or 'withdraw X'
+- Line 2: `N`
+- Next `N` lines: `deposit X` or `withdraw X`
 ### Output Format
 ```
 120
 ```
+### Example Walkthrough
+For the sample input, the account starts at 100. Depositing 50 raises it to 150, withdrawing 30 brings it to 120, and the withdrawal of 500 is ignored because only 120 is available, so the program prints `120`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1402,14 +1412,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Define a Stack class with push and pop methods backed by a list. Read N operations ('push X' or 'pop'), then print the remaining items from bottom to top separated by spaces, or 'empty' if the stack is empty.
+          <t>In the hostel mess, clean plates are stacked in a pile: a new plate always goes on top, and the next student always takes the plate from the top. Define a `Stack` class with `push` and `pop` methods backed by a list, working the same way. Read `N` operations (`push X` or `pop`), apply them in order, then print the remaining items from bottom to top separated by spaces, or `empty` if the stack is empty.
 ### Input Format
-- Line 1: N
-- Next N lines: 'push X' or 'pop'
+- Line 1: `N`
+- Next `N` lines: `push X` or `pop`
 ### Output Format
 ```
 1 3
 ```
+### Example Walkthrough
+For the sample input, `push 1` and `push 2` build the stack `1 2` from bottom to top. The `pop` removes the top item 2, and `push 3` places 3 on top, leaving `1 3`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1580,13 +1592,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Define a Circle class with methods area() and circumference() (use 3.14 for pi). Read a radius and print the area and circumference, each rounded to 2 decimal places, separated by a space.
+          <t>The photography club is designing circular badges for its members and needs to know each badge's area (for printing) and circumference (for the metal rim). Define a `Circle` class with methods `area()` and `circumference()`, using `3.14` for pi. Read a radius from input, create a `Circle` object, and print the area and circumference, each rounded to 2 decimal places, separated by a space.
 ### Input Format
 - Line 1: Radius
 ### Output Format
 ```
 3.14 6.28
 ```
+### Example Walkthrough
+For the sample input, the radius is 1. The area is 3.14 x 1 x 1 = 3.14 and the circumference is 2 x 3.14 x 1 = 6.28, so the program prints `3.14 6.28`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1731,17 +1745,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Define a BankAccount class where withdraw returns whether it succeeded. Read a starting balance and N operations ('deposit X' or 'withdraw X'). After each operation print the new balance, or 'Denied' if a withdrawal was refused for insufficient funds.
+          <t>An ATM near the college prints the new balance after every transaction, and if someone tries to withdraw more than they have, the slip shows `Denied` instead. Define a `BankAccount` class where the `withdraw` method returns whether it succeeded. Read a starting balance and `N` operations (`deposit X` or `withdraw X`). After each operation print the new balance, or `Denied` if a withdrawal was refused for insufficient funds.
 ### Input Format
 - Line 1: Starting balance
-- Line 2: N
-- Next N lines: 'deposit X' or 'withdraw X'
+- Line 2: `N`
+- Next `N` lines: `deposit X` or `withdraw X`
 ### Output Format
 ```
 150
 Denied
 50
 ```
+### Example Walkthrough
+For the sample input, the account starts at 100. Depositing 50 makes it 150 (printed), withdrawing 200 fails because only 150 is available (so `Denied` is printed), and withdrawing 100 succeeds, leaving 50 (printed).
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1921,13 +1937,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Define a Widget class that uses a class-level counter to track how many Widgets have been created, incremented in __init__. Read N, create N Widgets, and print how many exist.
+          <t>A stall at the college fest makes handmade keychains, and the organisers want the keychain 'blueprint' itself to keep count of how many have been produced so far. Define a `Widget` class that uses a class-level counter to track how many Widgets have been created, incremented inside `__init__`. Read `N` from input, create `N` `Widget` objects, and print how many exist.
 ### Input Format
-- Line 1: N
+- Line 1: `N`
 ### Output Format
 ```
 5
 ```
+### Example Walkthrough
+For the sample input, `N` is 5. Each time a `Widget` is created, `__init__` adds 1 to the shared class-level counter, so after creating 5 Widgets the counter holds 5 and the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -2071,7 +2089,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Define a Vector class with methods to add another vector and to compute the dot product. Read two vectors of equal length (space-separated), print their sum on one line and their dot product on the next.
+          <t>In the physics lab, two forces acting on an object are written as vectors, and Nisha needs both their combined effect (the sum) and their dot product for her practical record. Define a `Vector` class with methods to add another vector and to compute the dot product. Read two vectors of equal length (space-separated numbers) from input, then print their sum on one line and their dot product on the next.
 ### Input Format
 - Line 1: First vector
 - Line 2: Second vector
@@ -2080,6 +2098,8 @@
 5 7 9
 32
 ```
+### Example Walkthrough
+For the sample input, the vectors are `1 2 3` and `4 5 6`. Adding them position by position gives 1+4, 2+5, 3+6 = `5 7 9`, and the dot product is 1x4 + 2x5 + 3x6 = 4 + 10 + 18 = `32`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>

--- a/content/Question Bank/Coding Questions/Unit 9 - Basic Object-Oriented Programming/Unit 9 - Basic Object-Oriented Programming - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 9 - Basic Object-Oriented Programming/Unit 9 - Basic Object-Oriented Programming - Coding Questions.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Define a Counter class that starts at 0 and has an increment() method. Read N, increment a Counter N times, and print its final count.
+          <t>Define a Counter class that starts at 0 and has an `increment()` method. Read N, increment a Counter N times, and print its final count.
 ### Input Format
 - Line 1: N, the number of clicks
 ### Output Format
@@ -2561,7 +2561,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Define a BankAccount class with a balance and a deposit(amount) method. Read a starting balance and a deposit amount, apply the deposit, and print the new balance.
+          <t>Define a BankAccount class with a balance and a `deposit(amount)` method. Read a starting balance and a deposit amount, apply the deposit, and print the new balance.
 ### Input Format
 - Line 1: Starting balance
 - Line 2: Deposit amount
@@ -2721,7 +2721,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Define a Dog class that stores a name and has a bark() method returning '&lt;name&gt; says Woof'. Read a name and print the bark.
+          <t>Define a Dog class that stores a name and has a `bark()` method returning '&lt;name&gt; says Woof'. Read a name and print the bark.
 ### Input Format
 - Line 1: The dog's name
 ### Output Format
@@ -2869,7 +2869,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Define a Book class that stores a title and an author and has a method describe() returning '&lt;title&gt; by &lt;author&gt;'. Read a title and an author and print the description.
+          <t>Define a Book class that stores a title and an author and has a method `describe()` returning '&lt;title&gt; by &lt;author&gt;'. Read a title and an author and print the description.
 ### Input Format
 - Line 1: Title
 - Line 2: Author
@@ -3028,7 +3028,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Define a Thermometer class that stores a Celsius temperature and has a method to_fahrenheit() using F = C * 9 / 5 + 32. Read a Celsius value and print the Fahrenheit value rounded to 1 decimal place.
+          <t>Define a Thermometer class that stores a Celsius temperature and has a method `to_fahrenheit()` using F = C * 9 / 5 + 32. Read a Celsius value and print the Fahrenheit value rounded to 1 decimal place.
 ### Input Format
 - Line 1: Temperature in Celsius
 ### Output Format
@@ -3177,7 +3177,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Define a Rectangle class with methods area() and perimeter(). Read a width and height and print the area and perimeter separated by a space.
+          <t>Define a Rectangle class with methods `area()` and `perimeter()`. Read a width and height and print the area and perimeter separated by a space.
 ### Input Format
 - Line 1: Width
 - Line 2: Height
@@ -3339,7 +3339,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Define a Student class that stores a name and a list of marks and has an average() method. Read a name, then a line of marks, and print '&lt;name&gt; &lt;average&gt;' with the average rounded to 2 decimal places.
+          <t>Define a Student class that stores a name and a list of marks and has an `average()` method. Read a name, then a line of marks, and print '&lt;name&gt; &lt;average&gt;' with the average rounded to 2 decimal places.
 ### Input Format
 - Line 1: Name
 - Line 2: Space-separated marks
@@ -3499,7 +3499,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Define a class that tracks the largest number it has seen through an add(value) method. Read a line of numbers, add each one, and print the largest.
+          <t>Define a class that tracks the largest number it has seen through an `add(value)` method. Read a line of numbers, add each one, and print the largest.
 ### Input Format
 - Line 1: Space-separated numbers
 ### Output Format
@@ -3651,7 +3651,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Define an Employee class with a salary and a give_raise(percent) method that increases the salary by that percentage. Read a salary and a percentage, apply the raise, and print the new salary rounded to 2 decimal places.
+          <t>Define an Employee class with a salary and a `give_raise(percent)` method that increases the salary by that percentage. Read a salary and a percentage, apply the raise, and print the new salary rounded to 2 decimal places.
 ### Input Format
 - Line 1: Salary
 - Line 2: Raise percentage
@@ -3811,7 +3811,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Define a Rectangle class with an area() method. Read two rectangles (each as a width and height on one line) and print 'First' if the first has the larger area, 'Second' if the second does, or 'Equal' if they match.
+          <t>Define a Rectangle class with an `area()` method. Read two rectangles (each as a width and height on one line) and print 'First' if the first has the larger area, 'Second' if the second does, or 'Equal' if they match.
 ### Input Format
 - Line 1: width1 height1
 - Line 2: width2 height2
@@ -3977,7 +3977,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Define a Cart class with an add(price, quantity) method and a total() method. Read N items, each with a name, price, and quantity, add them, and print the cart total.
+          <t>Define a Cart class with an `add(price, quantity)` method and a `total()` method. Read N items, each with a name, price, and quantity, add them, and print the cart total.
 ### Input Format
 - Line 1: N
 - Next N lines: 'name price quantity'
@@ -4143,7 +4143,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Define a Person class that stores weight (kg) and height (m) and has a bmi() method returning weight / (height * height). Read a weight and a height and print the BMI rounded to 1 decimal place.
+          <t>Define a Person class that stores weight (kg) and height (m) and has a `bmi()` method returning weight / (height * height). Read a weight and a height and print the BMI rounded to 1 decimal place.
 ### Input Format
 - Line 1: Weight in kg
 - Line 2: Height in m
@@ -4305,7 +4305,7 @@
           <t>Define a Student class that stores a name and marks and can report its total. Read N students, each with a name followed by three marks, and print the name and total of the top scorer (earliest one on a tie).
 ### Input Format
 - Line 1: N
-- Next N lines: 'name m1 m2 m3'
+- Next N lines: 'name `m1` `m2` `m3`'
 ### Output Format
 ```
 asha 270
@@ -4980,7 +4980,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Define an Employee class with a pay() method: hours up to 40 are paid at the normal rate, and any hours beyond 40 are paid at 1.5 times the rate. Read N employees, each with a name, hours, and hourly rate, and print 'name pay' for each.
+          <t>Define an Employee class with a `pay()` method: hours up to 40 are paid at the normal rate, and any hours beyond 40 are paid at 1.5 times the rate. Read N employees, each with a name, hours, and hourly rate, and print 'name pay' for each.
 ### Input Format
 - Line 1: N
 - Next N lines: 'name hours rate'
@@ -5154,7 +5154,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Define a Polynomial class that stores coefficients from the highest power down to the constant and has an evaluate(x) method. Read the coefficients on one line and a value x, then print the polynomial evaluated at x.
+          <t>Define a Polynomial class that stores coefficients from the highest power down to the constant and has an `evaluate(x)` method. Read the coefficients on one line and a value x, then print the polynomial evaluated at x.
 ### Input Format
 - Line 1: Space-separated coefficients (high power first)
 - Line 2: The value x

--- a/content/Question Bank/Coding Questions/Unit 9 - Basic Object-Oriented Programming/Unit 9 - Basic Object-Oriented Programming - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 9 - Basic Object-Oriented Programming/Unit 9 - Basic Object-Oriented Programming - Coding Questions.xlsx
@@ -7,7 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH31"/>
+  <dimension ref="A1:AH11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -621,22 +624,32 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>oop</t>
+          <t>object-oriented-programming-intro</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>classes-objects</t>
+          <t>modeling-with-classes</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -782,22 +795,32 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>oop</t>
+          <t>object-oriented-programming-intro</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>constructors</t>
+          <t>attributes-and-methods</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -941,22 +964,32 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>oop</t>
+          <t>object-oriented-programming-intro</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>attributes-methods</t>
+          <t>attributes-and-methods</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1092,22 +1125,32 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>oop</t>
+          <t>object-oriented-programming-intro</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>constructors</t>
+          <t>attributes-and-methods</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1254,22 +1297,32 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>oop</t>
+          <t>object-oriented-programming-intro</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>attributes-methods</t>
+          <t>modeling-with-classes</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1437,22 +1490,32 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>oop</t>
+          <t>object-oriented-programming-intro</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>attributes-methods</t>
+          <t>modeling-with-classes</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1616,22 +1679,32 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>oop</t>
+          <t>object-oriented-programming-intro</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>attributes-methods</t>
+          <t>attributes-and-methods</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1773,22 +1846,32 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>oop</t>
+          <t>object-oriented-programming-intro</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>attributes-methods</t>
+          <t>modeling-with-classes</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1932,10 +2015,505 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Python - Book Object</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Book Object. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Title
+### Output Format
+```
+Python 101
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>classes-and-objects</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Python 101</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Python 101</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Data Basics</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Data Basics</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>AI Today</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>AI Today</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Clean Code</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Clean Code</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Book</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Long Title Here</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Long Title Here</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>class Book: pass
+b=Book(); b.title=input(); print(b.title)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Student Method</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Student Method. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Name
+### Output Format
+```
+Hello Asha
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>attributes-and-methods</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Asha</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Hello Asha</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Rohan</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hello Rohan</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Meena</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hello Meena</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Kabir</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Hello Kabir</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Zoya</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Hello Zoya</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Dev Patel</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hello Dev Patel</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Hello S</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>class Student:
+ def greet(self): print("Hello", self.name)
+s=Student(); s.name=input(); s.greet()</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>Python - Count Instances</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>A stall at the college fest makes handmade keychains, and the organisers want the keychain 'blueprint' itself to keep count of how many have been produced so far. Define a `Widget` class that uses a class-level counter to track how many Widgets have been created, incremented inside `__init__`. Read `N` from input, create `N` `Widget` objects, and print how many exist.
 ### Input Format
@@ -1951,124 +2529,134 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>oop</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>classes-objects</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>classes-and-objects</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
+      <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="Q10" t="b">
+      <c r="Q2" t="b">
         <v>1</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>class Widget:
     count = 0
@@ -2081,13 +2669,13 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Vector Operations</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>In the physics lab, two forces acting on an object are written as vectors, and Nisha needs both their combined effect (the sum) and their dot product for her practical record. Define a `Vector` class with methods to add another vector and to compute the dot product. Read two vectors of equal length (space-separated numbers) from input, then print their sum on one line and their dot product on the next.
 ### Input Format
@@ -2105,138 +2693,148 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>oop</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>attributes-methods</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>modeling-with-classes</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
+      <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="Q11" t="b">
+      <c r="Q3" t="b">
         <v>1</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>1 2 3
 4 5 6</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>5 7 9
 32</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>1 0
 0 1</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>1 1
 0</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>2 2
 3 3</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>5 5
 12</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>0 0
 0 0</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>0 0
 0</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>-1 -2
 1 2</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>0 0
 -5</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>5
 5</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>10
 25</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>1 2 3 4 5
 5 4 3 2 1</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>6 6 6 6 6
 35</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>class Vector:
     def __init__(self, values):
@@ -2252,13 +2850,13 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Circle Area Class</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Define a Circle class with a radius and a method that returns its area (use 3.14 for pi). Read a radius and print the area rounded to 2 decimal places.
 ### Input Format
@@ -2267,129 +2865,141 @@
 ```
 3.14
 ```
+### Example Walkthrough
+In the sample, the radius is `1`. The area is `3.14 x 1 x 1 = 3.14`, so the program prints `3.14`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>oop</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>classes-objects</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>attributes-and-methods</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O12" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P12" t="b">
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="Q12" t="b">
+      <c r="Q4" t="b">
         <v>1</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>3.14</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>12.56</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>78.5</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>314.0</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>28.26</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>31400.0</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>class Circle:
     def __init__(self, radius):
@@ -2401,13 +3011,13 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Click Counter</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Define a Counter class that starts at 0 and has an `increment()` method. Read N, increment a Counter N times, and print its final count.
 ### Input Format
@@ -2416,129 +3026,141 @@
 ```
 5
 ```
+### Example Walkthrough
+In the sample, `N` is `5`. Incrementing the counter five times leaves it at `5`, so the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>oop</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>attributes-methods</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>attributes-and-methods</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O13" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P13" t="b">
+      <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="Q13" t="b">
+      <c r="Q5" t="b">
         <v>1</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>class Counter:
     def __init__(self):
@@ -2553,13 +3175,13 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Simple Deposit</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Define a BankAccount class with a balance and a `deposit(amount)` method. Read a starting balance and a deposit amount, apply the deposit, and print the new balance.
 ### Input Format
@@ -2569,136 +3191,148 @@
 ```
 150
 ```
+### Example Walkthrough
+In the sample, the starting balance is `100` and the deposit is `50`. Adding them gives `150`, so the program prints `150`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>oop</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>attributes-methods</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>attributes-and-methods</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O14" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P14" t="b">
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q14" t="b">
+      <c r="Q6" t="b">
         <v>1</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>100
 50</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>0
 200</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>500
 0</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>-50
 100</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>1000
 2000</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>class BankAccount:
     def __init__(self, balance):
@@ -2713,13 +3347,13 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Dog Bark</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Define a Dog class that stores a name and has a `bark()` method returning '&lt;name&gt; says Woof'. Read a name and print the bark.
 ### Input Format
@@ -2728,129 +3362,141 @@
 ```
 Rex says Woof
 ```
+### Example Walkthrough
+In the sample, the name is `Rex`. The bark method returns `Rex says Woof`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>oop</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>classes-objects</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>attributes-and-methods</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O15" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P15" t="b">
+      <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="Q15" t="b">
+      <c r="Q7" t="b">
         <v>1</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Rex says Woof</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Bruno</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Bruno says Woof</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Milo</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Milo says Woof</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>A says Woof</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>Fido</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Fido says Woof</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Z says Woof</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>Buddy</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Buddy says Woof</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>class Dog:
     def __init__(self, name):
@@ -2861,13 +3507,13 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Book Info</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Define a Book class that stores a title and an author and has a method `describe()` returning '&lt;title&gt; by &lt;author&gt;'. Read a title and an author and print the description.
 ### Input Format
@@ -2877,136 +3523,148 @@
 ```
 Python by Guido
 ```
+### Example Walkthrough
+In the sample, the title is `Python` and the author is `Guido`. The description method returns `Python by Guido`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>oop</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>attributes-methods</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>attributes-and-methods</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O16" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P16" t="b">
+      <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="Q16" t="b">
+      <c r="Q8" t="b">
         <v>1</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Python
 Guido</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>Python by Guido</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Domain Design
 Evans</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Domain Design by Evans</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>X
 Y</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>X by Y</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>A
 B</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>A by B</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>1984
 Orwell</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>1984 by Orwell</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>War and Peace
 Tolstoy</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>War and Peace by Tolstoy</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>C
 D</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>C by D</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>class Book:
     def __init__(self, title, author):
@@ -3020,13 +3678,13 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Python - Thermometer Object</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Define a Thermometer class that stores a Celsius temperature and has a method `to_fahrenheit()` using F = C * 9 / 5 + 32. Read a Celsius value and print the Fahrenheit value rounded to 1 decimal place.
 ### Input Format
@@ -3035,129 +3693,141 @@
 ```
 32.0
 ```
+### Example Walkthrough
+In the sample, the Celsius value is `0`. Applying the formula gives `0 x 9 / 5 + 32 = 32.0`, so the program prints `32.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>oop</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>attributes-methods</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>attributes-and-methods</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O17" t="b">
+      <c r="O9" t="b">
         <v>0</v>
       </c>
-      <c r="P17" t="b">
+      <c r="P9" t="b">
         <v>1</v>
       </c>
-      <c r="Q17" t="b">
+      <c r="Q9" t="b">
         <v>1</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>32.0</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>212.0</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>98.6</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>-40</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>-40.0</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>-273.15</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>-459.7</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>98.6</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>209.5</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1832.0</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>class Thermometer:
     def __init__(self, celsius):
@@ -3169,13 +3839,517 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Point Constructor</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Point Constructor. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: x
+- Line 2: y
+### Output Format
+```
+1 2
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>constructors</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1
+2</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1 2</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0
+0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>0 0</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>-1
+5</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>-1 5</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>10
+20</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>10 20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>7
+8</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>7 8</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>100
+-100</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>100 -100</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>3
+3</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>3 3</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>class Point:
+ def __init__(self,x,y): self.x=x; self.y=y
+p=Point(int(input()),int(input()))
+print(p.x,p.y)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Fan Speed</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Fan Speed. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Speed
+### Output Format
+```
+Speed: 1
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>attributes-and-methods</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Speed: 1</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Speed: 0</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Speed: 3</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Speed: 5</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Speed: 10</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Speed: -1</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Speed: 100</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>class Fan: pass
+f=Fan(); f.speed=int(input()); print("Speed:", f.speed)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Rectangle Area and Perimeter</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Define a Rectangle class with methods `area()` and `perimeter()`. Read a width and height and print the area and perimeter separated by a space.
 ### Input Format
@@ -3185,136 +4359,148 @@
 ```
 12 14
 ```
+### Example Walkthrough
+In the sample, the width is `3` and the height is `4`. The area is `3 x 4 = 12` and the perimeter is `2 x (3 + 4) = 14`, so the program prints `12 14`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>oop</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>attributes-methods</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>attributes-and-methods</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O18" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P18" t="b">
+      <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="Q18" t="b">
+      <c r="Q2" t="b">
         <v>1</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>3
 4</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12 14</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>5
 5</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>25 20</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>2
 10</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>20 24</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>1 4</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>0 10</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>7
 3</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>21 20</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>100
 100</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>10000 400</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>class Rectangle:
     def __init__(self, width, height):
@@ -3331,13 +4517,13 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Student Average</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Define a Student class that stores a name and a list of marks and has an `average()` method. Read a name, then a line of marks, and print '&lt;name&gt; &lt;average&gt;' with the average rounded to 2 decimal places.
 ### Input Format
@@ -3347,136 +4533,148 @@
 ```
 Asha 90.0
 ```
+### Example Walkthrough
+In the sample, the name is `Asha` with marks `90 90 90`. Their average is `90.0`, so the program prints `Asha 90.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>oop</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>attributes-methods</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>attributes-and-methods</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O19" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P19" t="b">
+      <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="Q19" t="b">
+      <c r="Q3" t="b">
         <v>1</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Asha
 80 90 100</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Asha 90.0</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Sam
 50</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Sam 50.0</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Bob
 60 70</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Bob 65.0</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Zoe
 0</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Zoe 0.0</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Ann
 100 100 100</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Ann 100.0</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>Ray
 1 2 3 4 5</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>Ray 3.0</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>Kim
 0 0 100</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>Kim 33.33</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>class Student:
     def __init__(self, name, marks):
@@ -3491,13 +4689,13 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Running Maximum</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Define a class that tracks the largest number it has seen through an `add(value)` method. Read a line of numbers, add each one, and print the largest.
 ### Input Format
@@ -3506,129 +4704,141 @@
 ```
 5
 ```
+### Example Walkthrough
+In the sample, the numbers are `3 1 4 1 5`. Adding each one in turn, the tracker ends up holding the largest value seen, `5`, so the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>oop</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>attributes-methods</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>modeling-with-classes</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O20" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P20" t="b">
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="Q20" t="b">
+      <c r="Q4" t="b">
         <v>1</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>3 1 4 1 5</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>-1 -2</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>-5 -3 -8</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>100 -100</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>class MaxTracker:
     def __init__(self):
@@ -3643,13 +4853,13 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Give a Raise</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Define an Employee class with a salary and a `give_raise(percent)` method that increases the salary by that percentage. Read a salary and a percentage, apply the raise, and print the new salary rounded to 2 decimal places.
 ### Input Format
@@ -3659,136 +4869,148 @@
 ```
 1100.0
 ```
+### Example Walkthrough
+In the sample, the salary is `1000` and the raise is `10` percent. Adding `10%` of `1000` gives `1000 + 100 = 1100.0`, so the program prints `1100.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>oop</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>attributes-methods</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>attributes-and-methods</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O21" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P21" t="b">
+      <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="Q21" t="b">
+      <c r="Q5" t="b">
         <v>1</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>1000
 10</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>1100.0</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>5000
 0</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>5000.0</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>2000
 50</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>3000.0</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>0
 10</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>1000
 100</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>2000.0</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1.01</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>10000
 25</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>12500.0</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>class Employee:
     def __init__(self, salary):
@@ -3803,13 +5025,13 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Bigger Rectangle</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Define a Rectangle class with an `area()` method. Read two rectangles (each as a width and height on one line) and print 'First' if the first has the larger area, 'Second' if the second does, or 'Equal' if they match.
 ### Input Format
@@ -3819,136 +5041,148 @@
 ```
 Second
 ```
+### Example Walkthrough
+In the sample, the first rectangle is `2 x 3` with area `6`, and the second is `3 x 4` with area `12`. Since the second area is larger, the program prints `Second`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>oop</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>attributes-methods</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>modeling-with-classes</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O22" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P22" t="b">
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q22" t="b">
+      <c r="Q6" t="b">
         <v>1</v>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>3 4
 5 5</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Second</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>6 2
 3 4</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Equal</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>10 10
 2 2</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>First</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>1 1
 1 1</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Equal</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0 5
 5 0</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Equal</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>100 1
 1 100</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>Equal</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>5 5
 5 5</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Equal</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>class Rectangle:
     def __init__(self, width, height):
@@ -3969,13 +5203,13 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Shopping Cart Total</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Define a Cart class with an `add(price, quantity)` method and a `total()` method. Read N items, each with a name, price, and quantity, add them, and print the cart total.
 ### Input Format
@@ -3985,126 +5219,138 @@
 ```
 70
 ```
+### Example Walkthrough
+In the sample, there are `2` items: `apple` at `10` each for `3` units (`30`), and `banana` at `20` each for `2` units (`40`). Adding them gives `70`, so the program prints `70`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>oop</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>attributes-methods</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>modeling-with-classes</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O23" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P23" t="b">
+      <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="Q23" t="b">
+      <c r="Q7" t="b">
         <v>1</v>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>2
 apple 10 3
 bread 20 2</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>1
 milk 15 1</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>2
 a 5 5
 b 1 10</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1
 free 0 5</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>1
 x 100 1</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>3
 a 1 1
@@ -4112,12 +5358,12 @@
 c 3 3</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>class Cart:
     def __init__(self):
@@ -4135,13 +5381,13 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - BMI Calculator</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Define a Person class that stores weight (kg) and height (m) and has a `bmi()` method returning weight / (height * height). Read a weight and a height and print the BMI rounded to 1 decimal place.
 ### Input Format
@@ -4151,136 +5397,148 @@
 ```
 22.9
 ```
+### Example Walkthrough
+In the sample, the weight is `70` kg and the height is `1.75` m. The BMI is `70 / (1.75 x 1.75) = 22.857...`, which rounds to `22.9`, so the program prints `22.9`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>oop</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>attributes-methods</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>attributes-and-methods</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O24" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P24" t="b">
+      <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="Q24" t="b">
+      <c r="Q8" t="b">
         <v>1</v>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>70
 1.75</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>22.9</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>60
 1.6</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>23.4</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>80
 2.0</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>50
 1.5</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>22.2</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>100
 2.0</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>45
 1.4</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>90
 1.8</t>
         </is>
       </c>
-      <c r="AE24" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>27.8</t>
         </is>
       </c>
-      <c r="AG24" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>class Person:
     def __init__(self, weight, height):
@@ -4294,15 +5552,687 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - Bank Deposit</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Bank Deposit. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Balance
+- Line 2: Deposit
+### Output Format
+```
+150.0
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>modeling-with-classes</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>100
+50</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0
+10</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>-5
+5</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>1000
+250</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>1250.0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>75
+0</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>1
+2</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>10
+-3</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>class BankAccount:
+ def __init__(self,b): self.balance=b
+ def deposit(self,a): self.balance+=a
+a=BankAccount(float(input())); a.deposit(float(input())); print(a.balance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Rectangle Object</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Rectangle Object. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Width
+- Line 2: Height
+### Output Format
+```
+6
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>attributes-and-methods</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2
+3</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>5
+5</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0
+10</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7
+8</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>-2
+4</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>1
+1</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>100
+2</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>class Rectangle:
+ def __init__(self,w,h): self.w=w; self.h=h
+ def area(self): return self.w*self.h
+r=Rectangle(int(input()),int(input())); print(r.area())</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Counter Class</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Counter Class. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+### Output Format
+```
+3
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>modeling-with-classes</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>class Counter:
+ def __init__(self): self.count=0
+ def inc(self): self.count+=1
+c=Counter()
+for _ in range(int(input())): c.inc()
+print(c.count)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Class Topper</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Define a Student class that stores a name and marks and can report its total. Read N students, each with a name followed by three marks, and print the name and total of the top scorer (earliest one on a tie).
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Define a Student class that stores a name and marks and can report its total. Read `N` students, each with a name followed by three marks, and print the name and total of the top scorer (earliest one on a tie).
 ### Input Format
 - Line 1: N
 - Next N lines: 'name `m1` `m2` `m3`'
@@ -4310,59 +6240,71 @@
 ```
 asha 270
 ```
+### Example Walkthrough
+In the sample, `N` is `2` with `asha 90 90 90` (total `270`) and `kabir 60 60 60` (total `180`). `asha` has the higher total, so the program prints `asha 270`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>oop</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>attributes-methods</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>modeling-with-classes</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O25" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P25" t="b">
+      <c r="P2" t="b">
         <v>1</v>
       </c>
-      <c r="Q25" t="b">
+      <c r="Q2" t="b">
         <v>1</v>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>3
 asha 80 90 100
@@ -4370,58 +6312,58 @@
 meera 90 90 90</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>asha 270</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>1
 sam 50 50 50</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>sam 150</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>2
 a 10 10 10
 b 20 20 20</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>b 60</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>2
 x 0 0 0
 y 0 0 0</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>x 0</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>1
 solo 100 100 100</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>solo 300</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>4
 a 1 1 1
@@ -4430,12 +6372,12 @@
 d 4 4 4</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>d 12</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>3
 p 50 50 50
@@ -4443,12 +6385,12 @@
 r 50 50 50</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>p 150</t>
         </is>
       </c>
-      <c r="AG25" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>class Student:
     def __init__(self, name, marks):
@@ -4467,13 +6409,13 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Fraction Addition</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Define a Fraction class with a method that adds another fraction and returns the result in lowest terms. Read two fractions written as 'a/b', add them, and print the reduced result as 'p/q'.
 ### Input Format
@@ -4483,136 +6425,148 @@
 ```
 5/6
 ```
+### Example Walkthrough
+In the sample, the fractions are `1/2` and `1/3`. Adding them gives `3/6 + 2/6 = 5/6`, already in lowest terms, so the program prints `5/6`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>oop</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>attributes-methods</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>modeling-with-classes</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O26" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P26" t="b">
+      <c r="P3" t="b">
         <v>1</v>
       </c>
-      <c r="Q26" t="b">
+      <c r="Q3" t="b">
         <v>1</v>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>1/2
 1/3</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>5/6</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>1/4
 1/4</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>2/3
 1/3</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>1/1
 1/1</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>2/1</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0/1
 1/2</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>1/6
 1/3</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>5/8
 3/8</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="AG26" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>import math
 class Fraction:
@@ -4633,13 +6587,13 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Inventory Manager</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Define an Inventory class that tracks item quantities with add and remove methods. Read N operations ('add item qty' or 'remove item qty'), then print each item with a positive quantity as 'item:qty', sorted by item name.
 ### Input Format
@@ -4651,59 +6605,71 @@
 banana:3
 cherry:4
 ```
+### Example Walkthrough
+In the sample, the three operations add `3` apples, `3` bananas, and `4` cherries. Sorted alphabetically, the program prints `apple:3`, `banana:3`, and `cherry:4`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>oop</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>attributes-methods</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>modeling-with-classes</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O27" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P27" t="b">
+      <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="Q27" t="b">
+      <c r="Q4" t="b">
         <v>1</v>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>4
 add apple 5
@@ -4712,26 +6678,26 @@
 add cherry 4</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>apple:3
 banana:3
 cherry:4</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>2
 add milk 2
 add milk 3</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>milk:5</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>3
 add a 5
@@ -4739,36 +6705,36 @@
 add b 1</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>a:3
 b:1</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>1
 add x 1</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>x:1</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>2
 add x 5
 remove x 5</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>5
 add a 10
@@ -4778,12 +6744,12 @@
 remove b 25</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>c:5</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>class Inventory:
     def __init__(self):
@@ -4806,13 +6772,13 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Time Adder</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Define a Time class storing hours and minutes with a method to add another Time, carrying minutes over 60 into hours. Read two times written as 'h:m', add them, and print the result as 'h:mm' (minutes always two digits).
 ### Input Format
@@ -4822,136 +6788,148 @@
 ```
 4:15
 ```
+### Example Walkthrough
+In the sample, the times are `2:45` and `1:30`. Adding the minutes gives `45 + 30 = 75`, which carries `1` hour and leaves `15` minutes; adding the hours gives `2 + 1 + 1 = 4`, so the program prints `4:15`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>oop</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>attributes-methods</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>modeling-with-classes</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O28" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P28" t="b">
+      <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="Q28" t="b">
+      <c r="Q5" t="b">
         <v>1</v>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>1:30
 2:45</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>4:15</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>0:50
 0:20</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>1:10</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>2:00
 3:00</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>5:00</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>0:0
 0:0</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>0:00</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>23:59
 0:1</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>24:00</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>5:45
 5:45</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>12:30
 1:45</t>
         </is>
       </c>
-      <c r="AE28" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>14:15</t>
         </is>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>class Time:
     def __init__(self, hours, minutes):
@@ -4972,13 +6950,13 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Payroll</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Define an Employee class with a `pay()` method: hours up to 40 are paid at the normal rate, and any hours beyond 40 are paid at 1.5 times the rate. Read N employees, each with a name, hours, and hourly rate, and print 'name pay' for each.
 ### Input Format
@@ -4989,129 +6967,141 @@
 asha 475
 kabir 800
 ```
+### Example Walkthrough
+In the sample, `asha` works `25` hours at a rate of `19`, earning `25 x 19 = 475`, and `kabir` works exactly `40` hours at a rate of `20`, earning `40 x 20 = 800`, so the program prints `asha 475` then `kabir 800`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>oop</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>attributes-methods</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>modeling-with-classes</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O29" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P29" t="b">
+      <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q29" t="b">
+      <c r="Q6" t="b">
         <v>1</v>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>2
 asha 45 10
 kabir 40 20</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>asha 475
 kabir 800</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>1
 sam 20 10</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>sam 200</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>2
 a 50 10
 b 30 10</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>a 550
 b 300</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>1
 zero 0 10</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>zero 0</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>1
 exact 40 15</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>exact 600</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>1
 max 60 20</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>max 1400</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>3
 a 10 10
@@ -5119,14 +7109,14 @@
 c 41 10</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>a 100
 b 400
 c 415</t>
         </is>
       </c>
-      <c r="AG29" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>class Employee:
     def __init__(self, name, hours, rate):
@@ -5146,13 +7136,13 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Polynomial Evaluation</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Define a Polynomial class that stores coefficients from the highest power down to the constant and has an `evaluate(x)` method. Read the coefficients on one line and a value x, then print the polynomial evaluated at x.
 ### Input Format
@@ -5162,136 +7152,148 @@
 ```
 11
 ```
+### Example Walkthrough
+In the sample, the coefficients are `1 2 3` and `x` is `2`. Evaluating step by step: `0 x 2 + 1 = 1`, then `1 x 2 + 2 = 4`, then `4 x 2 + 3 = 11`, so the program prints `11`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>oop</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>attributes-methods</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>modeling-with-classes</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O30" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P30" t="b">
+      <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="Q30" t="b">
+      <c r="Q7" t="b">
         <v>1</v>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>1 2 3
 2</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>2 0 1
 3</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>5
 10</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>1 0 0
 0</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>1 -2 1
 1</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>3 2 1 0
 -2</t>
         </is>
       </c>
-      <c r="AE30" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="AG30" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>class Polynomial:
     def __init__(self, coeffs):
@@ -5307,13 +7309,13 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Matrix Addition</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Define a Matrix class with a method to add another matrix of the same size. Read the size R and C, then two matrices, and print their sum row by row.
 ### Input Format
@@ -5325,59 +7327,71 @@
 6 8
 10 12
 ```
+### Example Walkthrough
+In the sample, the matrices are `2` by `2`: `1 2 / 3 4` and `5 6 / 7 8`. Adding them position by position gives `6 8` and `10 12`, which the program prints one row per line.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>oop</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>attributes-methods</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>modeling-with-classes</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O31" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P31" t="b">
+      <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="Q31" t="b">
+      <c r="Q8" t="b">
         <v>1</v>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>2 2
 1 2
@@ -5386,25 +7400,25 @@
 7 8</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>6 8
 10 12</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>1 1
 5
 7</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>2 3
 1 1 1
@@ -5413,25 +7427,25 @@
 4 4 4</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>4 4 4
 6 6 6</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>1 2
 0 0
 0 0</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>0 0</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>3 1
 1
@@ -5442,14 +7456,14 @@
 6</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>5
 7
 9</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>2 2
 -1 -2
@@ -5458,25 +7472,25 @@
 3 4</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>0 0
 0 0</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1 3
 1 2 3
 4 5 6</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>5 7 9</t>
         </is>
       </c>
-      <c r="AG31" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>class Matrix:
     def __init__(self, rows):
@@ -5494,6 +7508,482 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - Inventory Item</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Inventory Item. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Price
+- Line 2: Quantity
+### Output Format
+```
+30.0
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>modeling-with-classes</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>10
+3</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>5.5
+2</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0
+10</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>100
+0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>7.25
+4</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>-1
+5</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>-5.0</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>99.99
+1</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>99.99</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>class Item:
+ def __init__(self,p,q): self.price=p; self.qty=q
+ def total(self): return self.price*self.qty
+i=Item(float(input()),int(input())); print(i.total())</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Temperature Class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Temperature Class. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Celsius
+### Output Format
+```
+32.0
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>attributes-and-methods</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>98.6</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>212.0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>-40</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>30.2</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>class Temperature:
+ def __init__(self,c): self.c=c
+ def fahrenheit(self): return self.c*9/5+32
+t=Temperature(float(input())); print(t.fahrenheit())</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Student Average Class</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Student Average Class. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Marks
+### Output Format
+```
+85.0
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>object-oriented-programming-intro</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>modeling-with-classes</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>80 90</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0 50 100</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>10 20 30</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>5 5 5</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>-10 10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>99 100 98</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>class Student:
+ def __init__(self,m): self.marks=m
+ def average(self): return sum(self.marks)/len(self.marks)
+s=Student(list(map(int,input().split()))); print(s.average())</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content/Question Bank/Coding Questions/Unit 9 - Basic Object-Oriented Programming/Unit 9 - Basic Object-Oriented Programming - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 9 - Basic Object-Oriented Programming/Unit 9 - Basic Object-Oriented Programming - Coding Questions.xlsx
@@ -2020,16 +2020,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Book Object. Read the input values and print the required result exactly.
+          <t>A library catalog app creates a bare `Book` object and tags it with a title attribute on the fly, then displays the title back to confirm it was recorded correctly.
+Define an empty `Book` class (with no attributes defined up front). Create a `Book` object, set its `title` attribute to a name read from input, and print that attribute.
 ### Input Format
-- Line 1: Title
+- Line 1: Book title
 ### Output Format
 ```
 Python 101
 ```
+### Example Walkthrough
+In the sample, the title is `Python 101`. The program creates a `Book` object, sets its `title` attribute to `Python 101`, and prints that attribute, giving `Python 101`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The input is a valid line of text with no leading or trailing spaces.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2174,16 +2177,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Student Method. Read the input values and print the required result exactly.
+          <t>A classroom attendance app creates a `Student` object, sets its name, and calls a `greet` method that announces the student by name the moment they check in.
+Define a `Student` class with a `greet` method that prints `Hello` followed by the object's `name` attribute (separated by a space). Create a `Student` object, set its `name` attribute to a name read from input, and call `greet`.
 ### Input Format
-- Line 1: Name
+- Line 1: Student name
 ### Output Format
 ```
 Hello Asha
 ```
+### Example Walkthrough
+In the sample, the name is `Asha`. The program sets the `Student` object's `name` to `Asha` and calls `greet`, which prints `Hello Asha`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The input is a valid name with no leading or trailing spaces.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -3847,17 +3853,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Point Constructor. Read the input values and print the required result exactly.
+          <t>A drawing app represents every point placed on the canvas as a `Point` object, built with the x and y coordinates supplied at the moment it's created.
+Define a `Point` class whose constructor (`__init__`) takes `x` and `y` and stores them as attributes. Read two whole numbers, create a `Point` object with them, and print its `x` and `y` attributes separated by a space.
 ### Input Format
-- Line 1: x
-- Line 2: y
+- Line 1: x coordinate
+- Line 2: y coordinate
 ### Output Format
 ```
 1 2
 ```
+### Example Walkthrough
+In the sample, x is 1 and y is 2. The program creates `Point(1, 2)`, which stores `x=1` and `y=2`, and prints `1 2`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -4011,16 +4020,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Fan Speed. Read the input values and print the required result exactly.
+          <t>A smart-home app creates a bare `Fan` object and sets its speed attribute directly from a slider in the app, then reports the fan's current speed on the dashboard.
+Define an empty `Fan` class (with no attributes defined up front). Create a `Fan` object, set its `speed` attribute to a whole number read from input, and print `Speed:` followed by the speed.
 ### Input Format
-- Line 1: Speed
+- Line 1: Fan speed
 ### Output Format
 ```
 Speed: 1
 ```
+### Example Walkthrough
+In the sample, the speed is 1. The program creates a `Fan` object, sets its `speed` attribute to 1, and prints `Speed: 1`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -5560,17 +5572,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Bank Deposit. Read the input values and print the required result exactly.
+          <t>An ATM app models a bank account as an object with a starting balance and a `deposit` method that adds money to it; after a customer deposits cash, the app shows the account's updated balance.
+Define a `BankAccount` class whose constructor takes a starting `balance`, with a `deposit` method that adds an amount to `balance`. Read a starting balance and a deposit amount, create the account, call `deposit`, and print the resulting balance.
 ### Input Format
-- Line 1: Balance
-- Line 2: Deposit
+- Line 1: Starting balance
+- Line 2: Deposit amount
 ### Output Format
 ```
 150.0
 ```
+### Example Walkthrough
+In the sample, the starting balance is 100 and the deposit is 50. After calling `deposit(50)`, the balance becomes 100 + 50 = 150.0, which the program prints.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -5724,7 +5739,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Rectangle Object. Read the input values and print the required result exactly.
+          <t>A sticker-sheet printing service models each custom sticker order as a `Rectangle` object with a width and a height, and uses an `area` method to compute how much printable space is needed before quoting the price.
+Define a `Rectangle` class whose constructor takes a width `w` and height `h`, with an `area` method that returns `w * h`. Read a width and a height, create a `Rectangle` object, and print its area.
 ### Input Format
 - Line 1: Width
 - Line 2: Height
@@ -5732,9 +5748,11 @@
 ```
 6
 ```
+### Example Walkthrough
+In the sample, the width is 2 and the height is 3. The `Rectangle` object's `area` method returns 2 x 3 = 6, so the program prints `6`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -5888,16 +5906,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Counter Class. Read the input values and print the required result exactly.
+          <t>A gym turnstile app models the day's entry count as a `Counter` object that starts at zero, with an `inc` method that increases the count by one every time someone taps in; the display shows the total once everyone has tapped in for the day.
+Define a `Counter` class whose constructor sets a `count` attribute to 0, with an `inc` method that increases `count` by 1. Read a whole number N, call `inc` on a `Counter` object N times, and print the final `count`.
 ### Input Format
-- Line 1: N
+- Line 1: N, the number of taps
 ### Output Format
 ```
 3
 ```
+### Example Walkthrough
+In the sample, N is 3. Calling `inc` three times increases `count` from 0 to 1, then 2, then 3, so the program prints `3`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -7516,7 +7537,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Inventory Item. Read the input values and print the required result exactly.
+          <t>A retail point-of-sale system models each product line on a receipt as an `Item` object with a price and a quantity, and a `total` method that returns that line's total cost.
+Define an `Item` class whose constructor takes a `price` and a `qty` (quantity), with a `total` method that returns `price * qty`. Read a price and a quantity, create an `Item` object, and print its total.
 ### Input Format
 - Line 1: Price
 - Line 2: Quantity
@@ -7524,9 +7546,11 @@
 ```
 30.0
 ```
+### Example Walkthrough
+In the sample, the price is 10 and the quantity is 3. The `Item` object's `total` method returns 10 x 3 = 30.0, so the program prints `30.0`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -7680,16 +7704,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Temperature Class. Read the input values and print the required result exactly.
+          <t>A weather app models each reading as a `Temperature` object created from a Celsius value, with a `fahrenheit` method that converts and returns the equivalent Fahrenheit temperature for the app's international users.
+Define a `Temperature` class whose constructor takes a Celsius value `c`, with a `fahrenheit` method that returns `c * 9 / 5 + 32`. Read a Celsius value, create a `Temperature` object, and print the result of calling `fahrenheit` on it.
 ### Input Format
-- Line 1: Celsius
+- Line 1: Temperature in Celsius
 ### Output Format
 ```
 32.0
 ```
+### Example Walkthrough
+In the sample, the Celsius value is 0. The `Temperature` object's `fahrenheit` method returns 0 x 9 / 5 + 32 = 32.0, so the program prints `32.0`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -7836,16 +7863,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Student Average Class. Read the input values and print the required result exactly.
+          <t>A report-card app models a student as a `Student` object holding a list of test marks, with an `average` method that returns the student's overall average score for the term.
+Define a `Student` class whose constructor takes a list of marks, with an `average` method that returns the sum of the marks divided by how many there are. Read a line of space-separated whole numbers, create a `Student` object with them, and print the result of calling `average` on it.
 ### Input Format
-- Line 1: Marks
+- Line 1: Space-separated marks
 ### Output Format
 ```
 85.0
 ```
+### Example Walkthrough
+In the sample, the marks are `80 90`. The `Student` object's `average` method returns (80 + 90) / 2 = 85.0, so the program prints `85.0`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- All numeric inputs are valid whole numbers in the ranges implied by the examples.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">

--- a/content/Question Bank/Coding Questions/Unit 9 - Basic Object-Oriented Programming/Unit 9 - Basic Object-Oriented Programming - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 9 - Basic Object-Oriented Programming/Unit 9 - Basic Object-Oriented Programming - Coding Questions.xlsx
@@ -7,10 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - Coding - Unit 9" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH11"/>
+  <dimension ref="A1:AH41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,18 +597,11 @@
       <c r="B2" t="inlineStr">
         <is>
           <t>Sneha is putting up a poster for the college fest and needs to know how much space it will cover on the notice board so she can buy the right amount of chart paper. Define a `Rectangle` class that stores a width and a height and has a method that returns its area (width times height). Read a width and a height from input, create a `Rectangle` object, and print its area.
-### Input Format
-- Line 1: Width
-- Line 2: Height
-### Output Format
-```
-12
-```
 ### Example Walkthrough
 For the sample input, the width is 3 and the height is 4. The `Rectangle` object stores these values, and its area method returns 3 x 4 = 12, so the program prints `12`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -752,13 +742,13 @@
         <is>
           <t>class Rectangle:
     def __init__(self, width, height):
-        self.width = width
-        self.height = height
+        self.width = width      # store width as an attribute on this object
+        self.height = height    # store height as an attribute on this object
     def area(self):
-        return self.width * self.height
+        return self.width * self.height   # self gives access to this object's own width/height
 w = int(input())
 h = int(input())
-print(Rectangle(w, h).area())</t>
+print(Rectangle(w, h).area())   # create an object, then call a method on it</t>
         </is>
       </c>
     </row>
@@ -771,18 +761,11 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>For the campus treasure hunt, every clue location is marked as a point on a grid map of the college. The organisers need a neat way to store and display each location. Define a `Point` class that stores `x` and `y` coordinates. Read `x` and `y` from input, create a `Point` object, and print it in the form `(x, y)`.
-### Input Format
-- Line 1: `x`
-- Line 2: `y`
-### Output Format
-```
-(3, 4)
-```
 ### Example Walkthrough
 For the sample input, `x` is 3 and `y` is 4. The `Point` object stores both coordinates, and printing it in the required form gives `(3, 4)`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -923,12 +906,12 @@
         <is>
           <t>class Point:
     def __init__(self, x, y):
-        self.x = x
-        self.y = y
+        self.x = x    # __init__ runs automatically when Point(...) is called
+        self.y = y    # store y as an attribute on this specific object
 x = int(input())
 y = int(input())
-p = Point(x, y)
-print(f"({p.x}, {p.y})")</t>
+p = Point(x, y)           # create a Point object with its own x and y
+print(f"({p.x}, {p.y})")  # access the object's attributes with dot notation</t>
         </is>
       </c>
     </row>
@@ -941,17 +924,11 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>On the first day of the semester, every student in the Python lab introduces themselves with a short greeting shown on the projector. Define a `Student` class that stores a name and has a method `greet()` that returns `Hi, I am &lt;name&gt;`. Read a name from input, create a `Student` object, and print the greeting.
-### Input Format
-- Line 1: A name
-### Output Format
-```
-Hi, I am Asha
-```
 ### Example Walkthrough
 For the sample input, the name is `Asha`. The `Student` object stores this name, and `greet()` returns `Hi, I am Asha`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1085,10 +1062,10 @@
         <is>
           <t>class Student:
     def __init__(self, name):
-        self.name = name
+        self.name = name   # save name on the object so methods can use it later
     def greet(self):
-        return f"Hi, I am {self.name}"
-print(Student(input()).greet())</t>
+        return f"Hi, I am {self.name}"   # self refers to the object calling greet()
+print(Student(input()).greet())   # create the object and call its method in one line</t>
         </is>
       </c>
     </row>
@@ -1101,18 +1078,11 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>Rohan is listing his family's old car on a second-hand vehicle website, and every listing shows the year followed by the brand. Define a `Car` class that stores a brand and a year and has a method `describe()` that returns `&lt;year&gt; &lt;brand&gt;`. Read a brand and a year from input, create a `Car` object, and print the description.
-### Input Format
-- Line 1: Brand
-- Line 2: Year
-### Output Format
-```
-2020 Toyota
-```
 ### Example Walkthrough
 For the sample input, the brand is `Toyota` and the year is 2020. The `Car` object stores both, and `describe()` returns `2020 Toyota`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1253,13 +1223,13 @@
         <is>
           <t>class Car:
     def __init__(self, brand, year):
-        self.brand = brand
-        self.year = year
+        self.brand = brand   # each Car object keeps its own brand
+        self.year = year     # and its own year
     def describe(self):
-        return f"{self.year} {self.brand}"
+        return f"{self.year} {self.brand}"   # build the description from this object's data
 brand = input()
 year = input()
-print(Car(brand, year).describe())</t>
+print(Car(brand, year).describe())   # instantiate Car, then call describe()</t>
         </is>
       </c>
     </row>
@@ -1272,19 +1242,11 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>Students in Anish's hostel use a prepaid mess card: they top it up with money and pay for meals from it, but the card simply refuses any payment larger than the balance. Define a `BankAccount` class with `deposit` and `withdraw` methods, where a `withdraw` that exceeds the balance is ignored. Read a starting balance, then `N` operations like `deposit 50` or `withdraw 30`, apply them in order, and print the final balance.
-### Input Format
-- Line 1: Starting balance
-- Line 2: `N`
-- Next `N` lines: `deposit X` or `withdraw X`
-### Output Format
-```
-120
-```
 ### Example Walkthrough
 For the sample input, the account starts at 100. Depositing 50 raises it to 150, withdrawing 30 brings it to 120, and the withdrawal of 500 is ignored because only 120 is available, so the program prints `120`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1438,12 +1400,12 @@
         <is>
           <t>class BankAccount:
     def __init__(self, balance):
-        self.balance = balance
+        self.balance = balance   # each account object tracks its own balance
     def deposit(self, amount):
-        self.balance += amount
+        self.balance += amount   # update this object's balance, not a shared value
     def withdraw(self, amount):
         if amount &lt;= self.balance:
-            self.balance -= amount
+            self.balance -= amount   # only withdraw if funds are sufficient
 account = BankAccount(int(input()))
 n = int(input())
 for _ in range(n):
@@ -1466,18 +1428,11 @@
       <c r="B7" t="inlineStr">
         <is>
           <t>In the hostel mess, clean plates are stacked in a pile: a new plate always goes on top, and the next student always takes the plate from the top. Define a `Stack` class with `push` and `pop` methods backed by a list, working the same way. Read `N` operations (`push X` or `pop`), apply them in order, then print the remaining items from bottom to top separated by spaces, or `empty` if the stack is empty.
-### Input Format
-- Line 1: `N`
-- Next `N` lines: `push X` or `pop`
-### Output Format
-```
-1 3
-```
 ### Example Walkthrough
 For the sample input, `push 1` and `push 2` build the stack `1 2` from bottom to top. The `pop` removes the top item 2, and `push 3` places 3 on top, leaving `1 3`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1629,12 +1584,12 @@
         <is>
           <t>class Stack:
     def __init__(self):
-        self.items = []
+        self.items = []   # each Stack object starts with its own empty list
     def push(self, value):
-        self.items.append(value)
+        self.items.append(value)   # add to the top of this object's list
     def pop(self):
         if self.items:
-            self.items.pop()
+            self.items.pop()   # remove from the top only if not empty
 stack = Stack()
 n = int(input())
 for _ in range(n):
@@ -1656,17 +1611,11 @@
       <c r="B8" t="inlineStr">
         <is>
           <t>The photography club is designing circular badges for its members and needs to know each badge's area (for printing) and circumference (for the metal rim). Define a `Circle` class with methods `area()` and `circumference()`, using `3.14` for pi. Read a radius from input, create a `Circle` object, and print the area and circumference, each rounded to 2 decimal places, separated by a space.
-### Input Format
-- Line 1: Radius
-### Output Format
-```
-3.14 6.28
-```
 ### Example Walkthrough
 For the sample input, the radius is 1. The area is 3.14 x 1 x 1 = 3.14 and the circumference is 2 x 3.14 x 1 = 6.28, so the program prints `3.14 6.28`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1800,13 +1749,13 @@
         <is>
           <t>class Circle:
     def __init__(self, radius):
-        self.radius = radius
+        self.radius = radius   # store radius so both methods can reuse it
     def area(self):
-        return 3.14 * self.radius * self.radius
+        return 3.14 * self.radius * self.radius   # self.radius belongs to this object
     def circumference(self):
-        return 2 * 3.14 * self.radius
+        return 2 * 3.14 * self.radius   # reuses the same stored radius
 c = Circle(int(input()))
-print(round(c.area(), 2), round(c.circumference(), 2))</t>
+print(round(c.area(), 2), round(c.circumference(), 2))   # call two methods on one object</t>
         </is>
       </c>
     </row>
@@ -1819,21 +1768,11 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>An ATM near the college prints the new balance after every transaction, and if someone tries to withdraw more than they have, the slip shows `Denied` instead. Define a `BankAccount` class where the `withdraw` method returns whether it succeeded. Read a starting balance and `N` operations (`deposit X` or `withdraw X`). After each operation print the new balance, or `Denied` if a withdrawal was refused for insufficient funds.
-### Input Format
-- Line 1: Starting balance
-- Line 2: `N`
-- Next `N` lines: `deposit X` or `withdraw X`
-### Output Format
-```
-150
-Denied
-50
-```
 ### Example Walkthrough
 For the sample input, the account starts at 100. Depositing 50 makes it 150 (printed), withdrawing 200 fails because only 150 is available (so `Denied` is printed), and withdrawing 100 succeeds, leaving 50 (printed).
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1987,13 +1926,13 @@
         <is>
           <t>class BankAccount:
     def __init__(self, balance):
-        self.balance = balance
+        self.balance = balance   # each account object keeps its own balance
     def deposit(self, amount):
         self.balance += amount
         return True
     def withdraw(self, amount):
         if amount &gt; self.balance:
-            return False
+            return False   # signal failure instead of changing the balance
         self.balance -= amount
         return True
 account = BankAccount(int(input()))
@@ -2005,7 +1944,7 @@
         account.deposit(amount)
         print(account.balance)
     else:
-        if account.withdraw(amount):
+        if account.withdraw(amount):   # check the returned success flag
             print(account.balance)
         else:
             print("Denied")</t>
@@ -2022,17 +1961,11 @@
         <is>
           <t>A library catalog app creates a bare `Book` object and tags it with a title attribute on the fly, then displays the title back to confirm it was recorded correctly.
 Define an empty `Book` class (with no attributes defined up front). Create a `Book` object, set its `title` attribute to a name read from input, and print that attribute.
-### Input Format
-- Line 1: Book title
-### Output Format
-```
-Python 101
-```
 ### Example Walkthrough
 In the sample, the title is `Python 101`. The program creates a `Book` object, sets its `title` attribute to `Python 101`, and prints that attribute, giving `Python 101`.
 ### Constraints
 - The input is a valid line of text with no leading or trailing spaces.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2164,8 +2097,8 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>class Book: pass
-b=Book(); b.title=input(); print(b.title)</t>
+          <t>class Book: pass   # empty class body; objects can still get attributes later
+b=Book(); b.title=input(); print(b.title)   # attribute added directly to this object, not the class</t>
         </is>
       </c>
     </row>
@@ -2179,17 +2112,11 @@
         <is>
           <t>A classroom attendance app creates a `Student` object, sets its name, and calls a `greet` method that announces the student by name the moment they check in.
 Define a `Student` class with a `greet` method that prints `Hello` followed by the object's `name` attribute (separated by a space). Create a `Student` object, set its `name` attribute to a name read from input, and call `greet`.
-### Input Format
-- Line 1: Student name
-### Output Format
-```
-Hello Asha
-```
 ### Example Walkthrough
 In the sample, the name is `Asha`. The program sets the `Student` object's `name` to `Asha` and calls `greet`, which prints `Hello Asha`.
 ### Constraints
 - The input is a valid name with no leading or trailing spaces.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2322,533 +2249,333 @@
       <c r="AG11" t="inlineStr">
         <is>
           <t>class Student:
- def greet(self): print("Hello", self.name)
-s=Student(); s.name=input(); s.greet()</t>
+ def greet(self): print("Hello", self.name)   # self.name works because it's set on the object below
+s=Student(); s.name=input(); s.greet()   # attribute added after creation, then the method reads it</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Python - Count Instances</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>A stall at the college fest makes handmade keychains, and the organisers want the keychain 'blueprint' itself to keep count of how many have been produced so far. Define a `Widget` class that uses a class-level counter to track how many Widgets have been created, incremented inside `__init__`. Read `N` from input, create `N` `Widget` objects, and print how many exist.
-### Input Format
-- Line 1: `N`
-### Output Format
-```
-5
-```
 ### Example Walkthrough
 For the sample input, `N` is 5. Each time a `Widget` is created, `__init__` adds 1 to the shared class-level counter, so after creating 5 Widgets the counter holds 5 and the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>classes-and-objects</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O12" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG12" t="inlineStr">
         <is>
           <t>class Widget:
-    count = 0
+    count = 0   # class attribute: shared by all Widget objects, not per-instance
     def __init__(self):
-        Widget.count += 1
+        Widget.count += 1   # every new object increments the shared class counter
 n = int(input())
 for _ in range(n):
-    Widget()
+    Widget()   # __init__ runs automatically each time a Widget is created
 print(Widget.count)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Python - Vector Operations</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>In the physics lab, two forces acting on an object are written as vectors, and Nisha needs both their combined effect (the sum) and their dot product for her practical record. Define a `Vector` class with methods to add another vector and to compute the dot product. Read two vectors of equal length (space-separated numbers) from input, then print their sum on one line and their dot product on the next.
-### Input Format
-- Line 1: First vector
-- Line 2: Second vector
-### Output Format
-```
-5 7 9
-32
-```
 ### Example Walkthrough
 For the sample input, the vectors are `1 2 3` and `4 5 6`. Adding them position by position gives 1+4, 2+5, 3+6 = `5 7 9`, and the dot product is 1x4 + 2x5 + 3x6 = 4 + 10 + 18 = `32`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>modeling-with-classes</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O13" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P13" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>1 2 3
 4 5 6</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>5 7 9
 32</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>1 0
 0 1</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>1 1
 0</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>2 2
 3 3</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>5 5
 12</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>0 0
 0 0</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>0 0
 0</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>-1 -2
 1 2</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>0 0
 -5</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>5
 5</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>10
 25</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>1 2 3 4 5
 5 4 3 2 1</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE13" t="inlineStr">
         <is>
           <t>6 6 6 6 6
 35</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG13" t="inlineStr">
         <is>
           <t>class Vector:
     def __init__(self, values):
-        self.values = values
+        self.values = values   # each Vector object stores its own list of numbers
     def add(self, other):
-        return Vector([a + b for a, b in zip(self.values, other.values)])
+        return Vector([a + b for a, b in zip(self.values, other.values)])   # combine two objects' data
     def dot(self, other):
-        return sum(a * b for a, b in zip(self.values, other.values))
+        return sum(a * b for a, b in zip(self.values, other.values))   # self and other are separate objects
 v1 = Vector(list(map(int, input().split())))
 v2 = Vector(list(map(int, input().split())))
 print(*v1.add(v2).values)
@@ -2856,323 +2583,311 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Python - Circle Area Class</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Define a Circle class with a radius and a method that returns its area (use 3.14 for pi). Read a radius and print the area rounded to 2 decimal places.
-### Input Format
-- Line 1: Radius
-### Output Format
-```
-3.14
-```
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>A landscaping company's mobile app lets a gardener quickly estimate how much sod is needed for a circular lawn, based only on the lawn's radius. Define a Circle class with a radius and a method that returns its area (use 3.14 for pi). Read a radius and print the area rounded to 2 decimal places.
 ### Example Walkthrough
 In the sample, the radius is `1`. The area is `3.14 x 1 x 1 = 3.14`, so the program prints `3.14`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>attributes-and-methods</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O14" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>3.14</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>12.56</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>78.5</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>314.0</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>28.26</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>31400.0</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG14" t="inlineStr">
         <is>
           <t>class Circle:
     def __init__(self, radius):
-        self.radius = radius
+        self.radius = radius   # store radius as an attribute on this object
     def area(self):
-        return 3.14 * self.radius * self.radius
+        return 3.14 * self.radius * self.radius   # self gives access to this object's radius
 r = int(input())
 print(round(Circle(r).area(), 2))</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Python - Click Counter</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Define a Counter class that starts at 0 and has an `increment()` method. Read N, increment a Counter N times, and print its final count.
-### Input Format
-- Line 1: N, the number of clicks
-### Output Format
-```
-5
-```
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>A fitness-tracker app counts every step a user takes by registering a click each time the phone's pedometer sensor detects a step. Define a Counter class that starts at 0 and has an `increment()` method. Read N, increment a Counter N times, and print its final count.
 ### Example Walkthrough
 In the sample, `N` is `5`. Incrementing the counter five times leaves it at `5`, so the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>attributes-and-methods</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O15" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG15" t="inlineStr">
         <is>
           <t>class Counter:
     def __init__(self):
-        self.count = 0
+        self.count = 0   # each Counter object starts its own count at 0
     def increment(self):
-        self.count += 1
+        self.count += 1   # updates only this object's count
 n = int(input())
 c = Counter()
 for _ in range(n):
@@ -3181,170 +2896,163 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Python - Simple Deposit</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Define a BankAccount class with a balance and a `deposit(amount)` method. Read a starting balance and a deposit amount, apply the deposit, and print the new balance.
-### Input Format
-- Line 1: Starting balance
-- Line 2: Deposit amount
-### Output Format
-```
-150
-```
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A college canteen's prepaid wallet app lets a student top up their balance before swiping it to pay for lunch. Define a BankAccount class with a balance and a `deposit(amount)` method. Read a starting balance and a deposit amount, apply the deposit, and print the new balance.
 ### Example Walkthrough
 In the sample, the starting balance is `100` and the deposit is `50`. Adding them gives `150`, so the program prints `150`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>attributes-and-methods</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O16" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>100
 50</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>0
 200</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>500
 0</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>-50
 100</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>1000
 2000</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG16" t="inlineStr">
         <is>
           <t>class BankAccount:
     def __init__(self, balance):
-        self.balance = balance
+        self.balance = balance   # store the starting balance on this object
     def deposit(self, amount):
-        self.balance += amount
+        self.balance += amount   # modify this object's own balance
 start = int(input())
 amount = int(input())
 account = BankAccount(start)
@@ -3353,1347 +3061,1115 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Python - Dog Bark</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Define a Dog class that stores a name and has a `bark()` method returning '&lt;name&gt; says Woof'. Read a name and print the bark.
-### Input Format
-- Line 1: The dog's name
-### Output Format
-```
-Rex says Woof
-```
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A pet-shelter's kiosk app lets volunteers introduce each dog up for adoption with a short, friendly greeting for visitors. Define a Dog class that stores a name and has a `bark()` method returning '&lt;name&gt; says Woof'. Read a name and print the bark.
 ### Example Walkthrough
 In the sample, the name is `Rex`. The bark method returns `Rex says Woof`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>attributes-and-methods</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O17" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P17" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>Rex says Woof</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Bruno</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Bruno says Woof</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Milo</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Milo says Woof</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>A says Woof</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>Fido</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>Fido says Woof</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>Z</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>Z says Woof</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>Buddy</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE17" t="inlineStr">
         <is>
           <t>Buddy says Woof</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG17" t="inlineStr">
         <is>
           <t>class Dog:
     def __init__(self, name):
-        self.name = name
+        self.name = name   # each Dog object remembers its own name
     def bark(self):
-        return f"{self.name} says Woof"
+        return f"{self.name} says Woof"   # self.name refers to this object's name
 print(Dog(input()).bark())</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Python - Book Info</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Define a Book class that stores a title and an author and has a method `describe()` returning '&lt;title&gt; by &lt;author&gt;'. Read a title and an author and print the description.
-### Input Format
-- Line 1: Title
-- Line 2: Author
-### Output Format
-```
-Python by Guido
-```
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>A library's digital catalog needs to generate a short description card for every book so members can browse titles at a glance. Define a Book class that stores a title and an author and has a method `describe()` returning '&lt;title&gt; by &lt;author&gt;'. Read a title and an author and print the description.
 ### Example Walkthrough
 In the sample, the title is `Python` and the author is `Guido`. The description method returns `Python by Guido`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>attributes-and-methods</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O18" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>1</v>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>Python
 Guido</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>Python by Guido</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Domain Design
 Evans</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Domain Design by Evans</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>X
 Y</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>X by Y</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>A
 B</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>A by B</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>1984
 Orwell</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>1984 by Orwell</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>War and Peace
 Tolstoy</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>War and Peace by Tolstoy</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>C
 D</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>C by D</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG18" t="inlineStr">
         <is>
           <t>class Book:
     def __init__(self, title, author):
-        self.title = title
+        self.title = title   # store both pieces of data on the object
         self.author = author
     def describe(self):
-        return f"{self.title} by {self.author}"
+        return f"{self.title} by {self.author}"   # combine this object's own attributes
 title = input()
 author = input()
 print(Book(title, author).describe())</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Python - Thermometer Object</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Define a Thermometer class that stores a Celsius temperature and has a method `to_fahrenheit()` using F = C * 9 / 5 + 32. Read a Celsius value and print the Fahrenheit value rounded to 1 decimal place.
-### Input Format
-- Line 1: Temperature in Celsius
-### Output Format
-```
-32.0
-```
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A campus weather station records readings in Celsius but needs to display them in Fahrenheit for the international-student dashboard. Define a Thermometer class that stores a Celsius temperature and has a method `to_fahrenheit()` using F = C * 9 / 5 + 32. Read a Celsius value and print the Fahrenheit value rounded to 1 decimal place.
 ### Example Walkthrough
 In the sample, the Celsius value is `0`. Applying the formula gives `0 x 9 / 5 + 32 = 32.0`, so the program prints `32.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>attributes-and-methods</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O19" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>1</v>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>32.0</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>212.0</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>98.6</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>-40</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>-40.0</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>-273.15</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>-459.7</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>98.6</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>209.5</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE19" t="inlineStr">
         <is>
           <t>1832.0</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AG19" t="inlineStr">
         <is>
           <t>class Thermometer:
     def __init__(self, celsius):
-        self.celsius = celsius
+        self.celsius = celsius   # store the Celsius value on this object
     def to_fahrenheit(self):
-        return self.celsius * 9 / 5 + 32
+        return self.celsius * 9 / 5 + 32   # convert using this object's stored value
 t = Thermometer(float(input()))
 print(round(t.to_fahrenheit(), 1))</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Python - Point Constructor</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>A drawing app represents every point placed on the canvas as a `Point` object, built with the x and y coordinates supplied at the moment it's created.
 Define a `Point` class whose constructor (`__init__`) takes `x` and `y` and stores them as attributes. Read two whole numbers, create a `Point` object with them, and print its `x` and `y` attributes separated by a space.
-### Input Format
-- Line 1: x coordinate
-- Line 2: y coordinate
-### Output Format
-```
-1 2
-```
 ### Example Walkthrough
 In the sample, x is 1 and y is 2. The program creates `Point(1, 2)`, which stores `x=1` and `y=2`, and prints `1 2`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>constructors</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O20" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>1
 2</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>1 2</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>0
 0</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>0 0</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>-1
 5</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>-1 5</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>10
 20</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>10 20</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>7
 8</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>7 8</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>100
 -100</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>100 -100</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>3
 3</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE20" t="inlineStr">
         <is>
           <t>3 3</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG20" t="inlineStr">
         <is>
           <t>class Point:
- def __init__(self,x,y): self.x=x; self.y=y
-p=Point(int(input()),int(input()))
+ def __init__(self,x,y): self.x=x; self.y=y   # constructor runs automatically, storing both coordinates
+p=Point(int(input()),int(input()))   # arguments are passed straight to __init__
 print(p.x,p.y)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Python - Fan Speed</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>A smart-home app creates a bare `Fan` object and sets its speed attribute directly from a slider in the app, then reports the fan's current speed on the dashboard.
 Define an empty `Fan` class (with no attributes defined up front). Create a `Fan` object, set its `speed` attribute to a whole number read from input, and print `Speed:` followed by the speed.
-### Input Format
-- Line 1: Fan speed
-### Output Format
-```
-Speed: 1
-```
 ### Example Walkthrough
 In the sample, the speed is 1. The program creates a `Fan` object, sets its `speed` attribute to 1, and prints `Speed: 1`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>attributes-and-methods</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O21" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>Speed: 1</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Speed: 0</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Speed: 3</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>Speed: 5</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>Speed: 10</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>Speed: -1</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE21" t="inlineStr">
         <is>
           <t>Speed: 100</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>class Fan: pass
-f=Fan(); f.speed=int(input()); print("Speed:", f.speed)</t>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>class Fan: pass   # empty class; attributes can still be attached to individual objects
+f=Fan(); f.speed=int(input()); print("Speed:", f.speed)   # speed belongs only to this Fan object</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Python - Rectangle Area and Perimeter</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Define a Rectangle class with methods `area()` and `perimeter()`. Read a width and height and print the area and perimeter separated by a space.
-### Input Format
-- Line 1: Width
-- Line 2: Height
-### Output Format
-```
-12 14
-```
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>A tile-flooring contractor's estimator app calculates how much tile and how much edge trim a rectangular room will need before quoting a job. Define a Rectangle class with methods `area()` and `perimeter()`. Read a width and height and print the area and perimeter separated by a space.
 ### Example Walkthrough
 In the sample, the width is `3` and the height is `4`. The area is `3 x 4 = 12` and the perimeter is `2 x (3 + 4) = 14`, so the program prints `12 14`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>attributes-and-methods</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O22" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>3
 4</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>12 14</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>5
 5</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>25 20</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>2
 10</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>20 24</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>1 4</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>0 10</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>7
 3</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>21 20</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>100
 100</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE22" t="inlineStr">
         <is>
           <t>10000 400</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG22" t="inlineStr">
         <is>
           <t>class Rectangle:
     def __init__(self, width, height):
-        self.width = width
+        self.width = width   # each Rectangle object stores its own dimensions
         self.height = height
     def area(self):
         return self.width * self.height
     def perimeter(self):
-        return 2 * (self.width + self.height)
+        return 2 * (self.width + self.height)   # reuses the same stored width and height
 w = int(input())
 h = int(input())
 r = Rectangle(w, h)
-print(r.area(), r.perimeter())</t>
+print(r.area(), r.perimeter())   # both methods read from the same object</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Python - Student Average</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Define a Student class that stores a name and a list of marks and has an `average()` method. Read a name, then a line of marks, and print '&lt;name&gt; &lt;average&gt;' with the average rounded to 2 decimal places.
-### Input Format
-- Line 1: Name
-- Line 2: Space-separated marks
-### Output Format
-```
-Asha 90.0
-```
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>A school's report-card generator needs to compute each student's average score across their subject marks before printing the final report. Define a Student class that stores a name and a list of marks and has an `average()` method. Read a name, then a line of marks, and print '&lt;name&gt; &lt;average&gt;' with the average rounded to 2 decimal places.
 ### Example Walkthrough
 In the sample, the name is `Asha` with marks `90 90 90`. Their average is `90.0`, so the program prints `Asha 90.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>attributes-and-methods</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O23" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>Asha
 80 90 100</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>Asha 90.0</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>Sam
 50</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>Sam 50.0</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>Bob
 60 70</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>Bob 65.0</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>Zoe
 0</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>Zoe 0.0</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>Ann
 100 100 100</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>Ann 100.0</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>Ray
 1 2 3 4 5</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>Ray 3.0</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>Kim
 0 0 100</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE23" t="inlineStr">
         <is>
           <t>Kim 33.33</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG23" t="inlineStr">
         <is>
           <t>class Student:
     def __init__(self, name, marks):
-        self.name = name
+        self.name = name    # store both name and marks on this object
         self.marks = marks
     def average(self):
-        return sum(self.marks) / len(self.marks)
+        return sum(self.marks) / len(self.marks)   # self.marks is this object's own list
 name = input()
 marks = list(map(int, input().split()))
 s = Student(name, marks)
@@ -4701,163 +4177,157 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Python - Running Maximum</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Define a class that tracks the largest number it has seen through an `add(value)` method. Read a line of numbers, add each one, and print the largest.
-### Input Format
-- Line 1: Space-separated numbers
-### Output Format
-```
-5
-```
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>An arcade's high-score board updates the day's top score every time a player finishes a round, keeping only the biggest score seen so far. Define a class that tracks the largest number it has seen through an `add(value)` method. Read a line of numbers, add each one, and print the largest.
 ### Example Walkthrough
 In the sample, the numbers are `3 1 4 1 5`. Adding each one in turn, the tracker ends up holding the largest value seen, `5`, so the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>modeling-with-classes</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O24" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>3 1 4 1 5</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>-1 -2</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>-5 -3 -8</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>1 2 3 4 5 6 7 8 9</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>100 -100</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG24" t="inlineStr">
         <is>
           <t>class MaxTracker:
     def __init__(self):
-        self.best = None
+        self.best = None   # each tracker object starts with no maximum seen yet
     def add(self, value):
         if self.best is None or value &gt; self.best:
-            self.best = value
+            self.best = value   # update this object's stored maximum
 tracker = MaxTracker()
 for x in map(int, input().split()):
     tracker.add(x)
@@ -4865,170 +4335,163 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Python - Give a Raise</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Define an Employee class with a salary and a `give_raise(percent)` method that increases the salary by that percentage. Read a salary and a percentage, apply the raise, and print the new salary rounded to 2 decimal places.
-### Input Format
-- Line 1: Salary
-- Line 2: Raise percentage
-### Output Format
-```
-1100.0
-```
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>An HR system needs to apply an approved raise to an employee's salary once the percentage increase is finalized. Define an Employee class with a salary and a `give_raise(percent)` method that increases the salary by that percentage. Read a salary and a percentage, apply the raise, and print the new salary rounded to 2 decimal places.
 ### Example Walkthrough
 In the sample, the salary is `1000` and the raise is `10` percent. Adding `10%` of `1000` gives `1000 + 100 = 1100.0`, so the program prints `1100.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>attributes-and-methods</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O25" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>1</v>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>1000
 10</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>1100.0</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>5000
 0</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>5000.0</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>2000
 50</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>3000.0</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>0
 10</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>1000
 100</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>2000.0</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>1.01</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>10000
 25</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE25" t="inlineStr">
         <is>
           <t>12500.0</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG25" t="inlineStr">
         <is>
           <t>class Employee:
     def __init__(self, salary):
-        self.salary = salary
+        self.salary = salary   # store starting salary on this object
     def give_raise(self, percent):
-        self.salary += self.salary * percent / 100
+        self.salary += self.salary * percent / 100   # modifies this object's own salary
 salary = int(input())
 percent = int(input())
 e = Employee(salary)
@@ -5037,174 +4500,167 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Python - Bigger Rectangle</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Define a Rectangle class with an `area()` method. Read two rectangles (each as a width and height on one line) and print 'First' if the first has the larger area, 'Second' if the second does, or 'Equal' if they match.
-### Input Format
-- Line 1: width1 height1
-- Line 2: width2 height2
-### Output Format
-```
-Second
-```
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>A carpentry workshop's cutting tool compares two rectangular wood panels to decide which one covers more surface area before sanding begins. Define a Rectangle class with an `area()` method. Read two rectangles (each as a width and height on one line) and print 'First' if the first has the larger area, 'Second' if the second does, or 'Equal' if they match.
 ### Example Walkthrough
 In the sample, the first rectangle is `2 x 3` with area `6`, and the second is `3 x 4` with area `12`. Since the second area is larger, the program prints `Second`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>modeling-with-classes</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O26" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>3 4
 5 5</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>Second</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>6 2
 3 4</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>Equal</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>10 10
 2 2</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>First</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>1 1
 1 1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>Equal</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>0 5
 5 0</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>Equal</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>100 1
 1 100</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>Equal</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>5 5
 5 5</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE26" t="inlineStr">
         <is>
           <t>Equal</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG26" t="inlineStr">
         <is>
           <t>class Rectangle:
     def __init__(self, width, height):
-        self.width = width
+        self.width = width   # each Rectangle object keeps its own dimensions
         self.height = height
     def area(self):
         return self.width * self.height
 w1, h1 = map(int, input().split())
 w2, h2 = map(int, input().split())
-a1 = Rectangle(w1, h1).area()
+a1 = Rectangle(w1, h1).area()   # two separate objects, each with its own data
 a2 = Rectangle(w2, h2).area()
 if a1 &gt; a2:
     print("First")
@@ -5215,154 +4671,147 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Python - Shopping Cart Total</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Define a Cart class with an `add(price, quantity)` method and a `total()` method. Read N items, each with a name, price, and quantity, add them, and print the cart total.
-### Input Format
-- Line 1: N
-- Next N lines: 'name price quantity'
-### Output Format
-```
-70
-```
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>A grocery store's self-checkout counter needs to tally up the bill as a shopper scans each item along with its price and quantity. Define a Cart class with an `add(price, quantity)` method and a `total()` method. Read N items, each with a name, price, and quantity, add them, and print the cart total.
 ### Example Walkthrough
 In the sample, there are `2` items: `apple` at `10` each for `3` units (`30`), and `banana` at `20` each for `2` units (`40`). Adding them gives `70`, so the program prints `70`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>modeling-with-classes</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O27" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>1</v>
+      </c>
+      <c r="R27" t="inlineStr">
         <is>
           <t>2
 apple 10 3
 bread 20 2</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>1
 milk 15 1</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>2
 a 5 5
 b 1 10</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>1
 free 0 5</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>1
 x 100 1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>3
 a 1 1
@@ -5370,18 +4819,18 @@
 c 3 3</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE27" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG27" t="inlineStr">
         <is>
           <t>class Cart:
     def __init__(self):
-        self.amount = 0
+        self.amount = 0   # each Cart object starts with its own running total
     def add(self, price, quantity):
-        self.amount += price * quantity
+        self.amount += price * quantity   # accumulate on this object's own total
     def total(self):
         return self.amount
 cart = Cart()
@@ -5393,939 +4842,719 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Python - BMI Calculator</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Define a Person class that stores weight (kg) and height (m) and has a `bmi()` method returning weight / (height * height). Read a weight and a height and print the BMI rounded to 1 decimal place.
-### Input Format
-- Line 1: Weight in kg
-- Line 2: Height in m
-### Output Format
-```
-22.9
-```
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>A college health center's annual check-up app calculates each student's Body Mass Index from their weight and height during the wellness screening. Define a Person class that stores weight (kg) and height (m) and has a `bmi()` method returning weight / (height * height). Read a weight and a height and print the BMI rounded to 1 decimal place.
 ### Example Walkthrough
 In the sample, the weight is `70` kg and the height is `1.75` m. The BMI is `70 / (1.75 x 1.75) = 22.857...`, which rounds to `22.9`, so the program prints `22.9`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>attributes-and-methods</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O28" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>70
 1.75</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>22.9</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>60
 1.6</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>23.4</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>80
 2.0</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>50
 1.5</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>22.2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>100
 2.0</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>45
 1.4</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>90
 1.8</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE28" t="inlineStr">
         <is>
           <t>27.8</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG28" t="inlineStr">
         <is>
           <t>class Person:
     def __init__(self, weight, height):
-        self.weight = weight
+        self.weight = weight   # store both measurements on this object
         self.height = height
     def bmi(self):
-        return self.weight / (self.height * self.height)
+        return self.weight / (self.height * self.height)   # uses this object's own weight and height
 weight = float(input())
 height = float(input())
 print(round(Person(weight, height).bmi(), 1))</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Python - Bank Deposit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>An ATM app models a bank account as an object with a starting balance and a `deposit` method that adds money to it; after a customer deposits cash, the app shows the account's updated balance.
 Define a `BankAccount` class whose constructor takes a starting `balance`, with a `deposit` method that adds an amount to `balance`. Read a starting balance and a deposit amount, create the account, call `deposit`, and print the resulting balance.
-### Input Format
-- Line 1: Starting balance
-- Line 2: Deposit amount
-### Output Format
-```
-150.0
-```
 ### Example Walkthrough
 In the sample, the starting balance is 100 and the deposit is 50. After calling `deposit(50)`, the balance becomes 100 + 50 = 150.0, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>modeling-with-classes</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O29" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>1</v>
+      </c>
+      <c r="R29" t="inlineStr">
         <is>
           <t>100
 50</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>0
 10</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>-5
 5</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>1000
 250</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>1250.0</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>75
 0</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>75.0</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>1
 2</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>10
 -3</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE29" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AG29" t="inlineStr">
         <is>
           <t>class BankAccount:
- def __init__(self,b): self.balance=b
- def deposit(self,a): self.balance+=a
+ def __init__(self,b): self.balance=b   # constructor stores the starting balance on the object
+ def deposit(self,a): self.balance+=a   # updates only this object's balance
 a=BankAccount(float(input())); a.deposit(float(input())); print(a.balance)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Python - Rectangle Object</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>A sticker-sheet printing service models each custom sticker order as a `Rectangle` object with a width and a height, and uses an `area` method to compute how much printable space is needed before quoting the price.
 Define a `Rectangle` class whose constructor takes a width `w` and height `h`, with an `area` method that returns `w * h`. Read a width and a height, create a `Rectangle` object, and print its area.
-### Input Format
-- Line 1: Width
-- Line 2: Height
-### Output Format
-```
-6
-```
 ### Example Walkthrough
 In the sample, the width is 2 and the height is 3. The `Rectangle` object's `area` method returns 2 x 3 = 6, so the program prints `6`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>attributes-and-methods</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O30" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R30" t="inlineStr">
         <is>
           <t>2
 3</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>5
 5</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>0
 10</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>7
 8</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>-2
 4</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>1
 1</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>100
 2</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG30" t="inlineStr">
         <is>
           <t>class Rectangle:
- def __init__(self,w,h): self.w=w; self.h=h
- def area(self): return self.w*self.h
+ def __init__(self,w,h): self.w=w; self.h=h   # store both dimensions as attributes on the object
+ def area(self): return self.w*self.h   # self gives access to this object's own w and h
 r=Rectangle(int(input()),int(input())); print(r.area())</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Python - Counter Class</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>A gym turnstile app models the day's entry count as a `Counter` object that starts at zero, with an `inc` method that increases the count by one every time someone taps in; the display shows the total once everyone has tapped in for the day.
 Define a `Counter` class whose constructor sets a `count` attribute to 0, with an `inc` method that increases `count` by 1. Read a whole number N, call `inc` on a `Counter` object N times, and print the final `count`.
-### Input Format
-- Line 1: N, the number of taps
-### Output Format
-```
-3
-```
 ### Example Walkthrough
 In the sample, N is 3. Calling `inc` three times increases `count` from 0 to 1, then 2, then 3, so the program prints `3`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>modeling-with-classes</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O31" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>1</v>
+      </c>
+      <c r="R31" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE31" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG31" t="inlineStr">
         <is>
           <t>class Counter:
- def __init__(self): self.count=0
- def inc(self): self.count+=1
+ def __init__(self): self.count=0   # every new Counter object starts at zero
+ def inc(self): self.count+=1   # increments only this object's own count
 c=Counter()
 for _ in range(int(input())): c.inc()
 print(c.count)</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Python - Class Topper</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Define a Student class that stores a name and marks and can report its total. Read `N` students, each with a name followed by three marks, and print the name and total of the top scorer (earliest one on a tie).
-### Input Format
-- Line 1: N
-- Next N lines: 'name `m1` `m2` `m3`'
-### Output Format
-```
-asha 270
-```
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>A college's exam cell wants to announce the topper of a class the moment all three subject marks are entered for every student. Define a Student class that stores a name and marks and can report its total. Read `N` students, each with a name followed by three marks, and print the name and total of the top scorer (earliest one on a tie).
 ### Example Walkthrough
 In the sample, `N` is `2` with `asha 90 90 90` (total `270`) and `kabir 60 60 60` (total `180`). `asha` has the higher total, so the program prints `asha 270`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>modeling-with-classes</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O32" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P32" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" t="inlineStr">
         <is>
           <t>3
 asha 80 90 100
@@ -6333,58 +5562,58 @@
 meera 90 90 90</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>asha 270</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>1
 sam 50 50 50</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>sam 150</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>2
 a 10 10 10
 b 20 20 20</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>b 60</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>2
 x 0 0 0
 y 0 0 0</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>x 0</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>1
 solo 100 100 100</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>solo 300</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>4
 a 1 1 1
@@ -6393,12 +5622,12 @@
 d 4 4 4</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>d 12</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>3
 p 50 50 50
@@ -6406,16 +5635,16 @@
 r 50 50 50</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE32" t="inlineStr">
         <is>
           <t>p 150</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG32" t="inlineStr">
         <is>
           <t>class Student:
     def __init__(self, name, marks):
-        self.name = name
+        self.name = name    # each Student object stores its own name and marks
         self.marks = marks
     def total(self):
         return sum(self.marks)
@@ -6423,182 +5652,175 @@
 best = None
 for _ in range(n):
     parts = input().split()
-    student = Student(parts[0], [int(m) for m in parts[1:]])
+    student = Student(parts[0], [int(m) for m in parts[1:]])   # a fresh object for each student
     if best is None or student.total() &gt; best.total():
-        best = student
+        best = student   # keep the object with the higher total, not just a number
 print(best.name, best.total())</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Python - Fraction Addition</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Define a Fraction class with a method that adds another fraction and returns the result in lowest terms. Read two fractions written as 'a/b', add them, and print the reduced result as 'p/q'.
-### Input Format
-- Line 1: First fraction 'a/b'
-- Line 2: Second fraction 'a/b'
-### Output Format
-```
-5/6
-```
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>A recipe app lets a home cook combine two fractional measurements, like half a cup of flour and a third of a cup of sugar, into a single reduced amount. Define a Fraction class with a method that adds another fraction and returns the result in lowest terms. Read two fractions written as 'a/b', add them, and print the reduced result as 'p/q'.
 ### Example Walkthrough
 In the sample, the fractions are `1/2` and `1/3`. Adding them gives `3/6 + 2/6 = 5/6`, already in lowest terms, so the program prints `5/6`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>modeling-with-classes</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O33" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P33" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" t="inlineStr">
         <is>
           <t>1/2
 1/3</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>5/6</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>1/4
 1/4</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>2/3
 1/3</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>1/1
 1/1</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>2/1</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>0/1
 1/2</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>1/6
 1/3</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>5/8
 3/8</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE33" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG33" t="inlineStr">
         <is>
           <t>import math
 class Fraction:
     def __init__(self, num, den):
-        self.num = num
+        self.num = num   # each Fraction object stores its own numerator and denominator
         self.den = den
     def add(self, other):
-        num = self.num * other.den + other.num * self.den
+        num = self.num * other.den + other.num * self.den   # combine self's data with other's data
         den = self.den * other.den
         g = math.gcd(num, den)
-        return Fraction(num // g, den // g)
+        return Fraction(num // g, den // g)   # add() returns a brand new Fraction object
 a = input().split("/")
 b = input().split("/")
 f1 = Fraction(int(a[0]), int(a[1]))
@@ -6608,89 +5830,80 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Python - Inventory Manager</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Define an Inventory class that tracks item quantities with add and remove methods. Read N operations ('add item qty' or 'remove item qty'), then print each item with a positive quantity as 'item:qty', sorted by item name.
-### Input Format
-- Line 1: N
-- Next N lines: 'add item qty' or 'remove item qty'
-### Output Format
-```
-apple:3
-banana:3
-cherry:4
-```
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>A hostel's store-room keeper logs every item that gets added to or issued out of stock, and needs a final tally of what remains. Define an Inventory class that tracks item quantities with add and remove methods. Read N operations ('add item qty' or 'remove item qty'), then print each item with a positive quantity as 'item:qty', sorted by item name.
 ### Example Walkthrough
 In the sample, the three operations add `3` apples, `3` bananas, and `4` cherries. Sorted alphabetically, the program prints `apple:3`, `banana:3`, and `cherry:4`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>modeling-with-classes</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O34" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34" t="inlineStr">
         <is>
           <t>4
 add apple 5
@@ -6699,26 +5912,26 @@
 add cherry 4</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>apple:3
 banana:3
 cherry:4</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>2
 add milk 2
 add milk 3</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>milk:5</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>3
 add a 5
@@ -6726,36 +5939,36 @@
 add b 1</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>a:3
 b:1</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>1
 add x 1</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>x:1</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>2
 add x 5
 remove x 5</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>5
 add a 10
@@ -6765,18 +5978,18 @@
 remove b 25</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE34" t="inlineStr">
         <is>
           <t>c:5</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG34" t="inlineStr">
         <is>
           <t>class Inventory:
     def __init__(self):
-        self.items = {}
+        self.items = {}   # each Inventory object keeps its own dictionary of items
     def add(self, item, qty):
-        self.items[item] = self.items.get(item, 0) + qty
+        self.items[item] = self.items.get(item, 0) + qty   # update this object's own data
     def remove(self, item, qty):
         self.items[item] = self.items.get(item, 0) - qty
 inv = Inventory()
@@ -6793,175 +6006,168 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Python - Time Adder</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Define a Time class storing hours and minutes with a method to add another Time, carrying minutes over 60 into hours. Read two times written as 'h:m', add them, and print the result as 'h:mm' (minutes always two digits).
-### Input Format
-- Line 1: First time 'h:m'
-- Line 2: Second time 'h:m'
-### Output Format
-```
-4:15
-```
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>A bus schedule app adds a journey's travel duration to its departure time to work out the expected arrival time, carrying extra minutes into hours. Define a Time class storing hours and minutes with a method to add another Time, carrying minutes over 60 into hours. Read two times written as 'h:m', add them, and print the result as 'h:mm' (minutes always two digits).
 ### Example Walkthrough
 In the sample, the times are `2:45` and `1:30`. Adding the minutes gives `45 + 30 = 75`, which carries `1` hour and leaves `15` minutes; adding the hours gives `2 + 1 + 1 = 4`, so the program prints `4:15`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>modeling-with-classes</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O35" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P35" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>1</v>
+      </c>
+      <c r="R35" t="inlineStr">
         <is>
           <t>1:30
 2:45</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>4:15</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>0:50
 0:20</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>1:10</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>2:00
 3:00</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>5:00</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>0:0
 0:0</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>0:00</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>23:59
 0:1</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>24:00</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>5:45
 5:45</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>12:30
 1:45</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE35" t="inlineStr">
         <is>
           <t>14:15</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG35" t="inlineStr">
         <is>
           <t>class Time:
     def __init__(self, hours, minutes):
-        self.hours = hours
+        self.hours = hours   # each Time object stores its own hours and minutes
         self.minutes = minutes
     def add(self, other):
-        total = self.minutes + other.minutes
+        total = self.minutes + other.minutes   # combine minutes from both objects
         carry = total // 60
         minutes = total % 60
         hours = self.hours + other.hours + carry
-        return Time(hours, minutes)
+        return Time(hours, minutes)   # add() returns a new Time object, doesn't change self
 a = input().split(":")
 b = input().split(":")
 t1 = Time(int(a[0]), int(a[1]))
@@ -6971,158 +6177,150 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Python - Payroll</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Define an Employee class with a `pay()` method: hours up to 40 are paid at the normal rate, and any hours beyond 40 are paid at 1.5 times the rate. Read N employees, each with a name, hours, and hourly rate, and print 'name pay' for each.
-### Input Format
-- Line 1: N
-- Next N lines: 'name hours rate'
-### Output Format
-```
-asha 475
-kabir 800
-```
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>A company's payroll system calculates each employee's weekly wage, paying overtime at 1.5 times the normal rate for any hours worked beyond 40. Define an Employee class with a `pay()` method: hours up to 40 are paid at the normal rate, and any hours beyond 40 are paid at 1.5 times the rate. Read N employees, each with a name, hours, and hourly rate, and print 'name pay' for each.
 ### Example Walkthrough
 In the sample, `asha` works `25` hours at a rate of `19`, earning `25 x 19 = 475`, and `kabir` works exactly `40` hours at a rate of `20`, earning `40 x 20 = 800`, so the program prints `asha 475` then `kabir 800`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>modeling-with-classes</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O36" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P36" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" t="inlineStr">
         <is>
           <t>2
 asha 45 10
 kabir 40 20</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>asha 475
 kabir 800</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>1
 sam 20 10</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>sam 200</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>2
 a 50 10
 b 30 10</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>a 550
 b 300</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>1
 zero 0 10</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>zero 0</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>1
 exact 40 15</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>exact 600</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>1
 max 60 20</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>max 1400</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>3
 a 10 10
@@ -7130,199 +6328,192 @@
 c 41 10</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE36" t="inlineStr">
         <is>
           <t>a 100
 b 400
 c 415</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG36" t="inlineStr">
         <is>
           <t>class Employee:
     def __init__(self, name, hours, rate):
-        self.name = name
+        self.name = name   # each Employee object stores its own name, hours, and rate
         self.hours = hours
         self.rate = rate
     def pay(self):
         if self.hours &lt;= 40:
-            return self.hours * self.rate
-        return 40 * self.rate + (self.hours - 40) * self.rate * 1.5
+            return self.hours * self.rate   # normal rate for up to 40 hours
+        return 40 * self.rate + (self.hours - 40) * self.rate * 1.5   # overtime hours pay 1.5x
 n = int(input())
 for _ in range(n):
     name, hours, rate = input().split()
-    e = Employee(name, int(hours), int(rate))
+    e = Employee(name, int(hours), int(rate))   # a new object for each employee
     pay = e.pay()
     print(name, int(pay) if pay == int(pay) else pay)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Python - Polynomial Evaluation</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Define a Polynomial class that stores coefficients from the highest power down to the constant and has an `evaluate(x)` method. Read the coefficients on one line and a value x, then print the polynomial evaluated at x.
-### Input Format
-- Line 1: Space-separated coefficients (high power first)
-- Line 2: The value x
-### Output Format
-```
-11
-```
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>An engineering calculator app evaluates a motion equation written as a polynomial at a given point in time to predict a value such as displacement. Define a Polynomial class that stores coefficients from the highest power down to the constant and has an `evaluate(x)` method. Read the coefficients on one line and a value x, then print the polynomial evaluated at x.
 ### Example Walkthrough
 In the sample, the coefficients are `1 2 3` and `x` is `2`. Evaluating step by step: `0 x 2 + 1 = 1`, then `1 x 2 + 2 = 4`, then `4 x 2 + 3 = 11`, so the program prints `11`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>modeling-with-classes</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O37" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P37" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>1</v>
+      </c>
+      <c r="R37" t="inlineStr">
         <is>
           <t>1 2 3
 2</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>2 0 1
 3</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>5
 10</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>0
 5</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>1 0 0
 0</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>1 -2 1
 1</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>3 2 1 0
 -2</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE37" t="inlineStr">
         <is>
           <t>-18</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG37" t="inlineStr">
         <is>
           <t>class Polynomial:
     def __init__(self, coeffs):
-        self.coeffs = coeffs
+        self.coeffs = coeffs   # store the coefficient list on this object
     def evaluate(self, x):
         result = 0
         for c in self.coeffs:
-            result = result * x + c
+            result = result * x + c   # uses self.coeffs, this object's own data
         return result
 coeffs = list(map(int, input().split()))
 x = int(input())
@@ -7330,89 +6521,80 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Python - Matrix Addition</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Define a Matrix class with a method to add another matrix of the same size. Read the size R and C, then two matrices, and print their sum row by row.
-### Input Format
-- Line 1: R and C separated by a space
-- Next R lines: first matrix rows
-- Next R lines: second matrix rows
-### Output Format
-```
-6 8
-10 12
-```
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>A grade-sheet tool needs to merge two sets of marks entered in a spreadsheet-style grid, such as internal and external marks, into one combined grid by adding matching cells. Define a Matrix class with a method to add another matrix of the same size. Read the size R and C, then two matrices, and print their sum row by row.
 ### Example Walkthrough
 In the sample, the matrices are `2` by `2`: `1 2 / 3 4` and `5 6 / 7 8`. Adding them position by position gives `6 8` and `10 12`, which the program prints one row per line.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>modeling-with-classes</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O38" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P38" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>1</v>
+      </c>
+      <c r="R38" t="inlineStr">
         <is>
           <t>2 2
 1 2
@@ -7421,25 +6603,25 @@
 7 8</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>6 8
 10 12</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>1 1
 5
 7</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>2 3
 1 1 1
@@ -7448,25 +6630,25 @@
 4 4 4</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>4 4 4
 6 6 6</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>1 2
 0 0
 0 0</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>0 0</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>3 1
 1
@@ -7477,14 +6659,14 @@
 6</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>5
 7
 9</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>2 2
 -1 -2
@@ -7493,34 +6675,34 @@
 3 4</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>0 0
 0 0</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>1 3
 1 2 3
 4 5 6</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE38" t="inlineStr">
         <is>
           <t>5 7 9</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG38" t="inlineStr">
         <is>
           <t>class Matrix:
     def __init__(self, rows):
-        self.rows = rows
+        self.rows = rows   # each Matrix object stores its own 2D list of rows
     def add(self, other):
         return Matrix([
             [a + b for a, b in zip(r1, r2)]
             for r1, r2 in zip(self.rows, other.rows)
-        ])
+        ])   # combines self's rows with other's rows into a new Matrix object
 r, c = map(int, input().split())
 m1 = [list(map(int, input().split())) for _ in range(r)]
 m2 = [list(map(int, input().split())) for _ in range(r)]
@@ -7529,487 +6711,468 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Python - Inventory Item</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>A retail point-of-sale system models each product line on a receipt as an `Item` object with a price and a quantity, and a `total` method that returns that line's total cost.
 Define an `Item` class whose constructor takes a `price` and a `qty` (quantity), with a `total` method that returns `price * qty`. Read a price and a quantity, create an `Item` object, and print its total.
-### Input Format
-- Line 1: Price
-- Line 2: Quantity
-### Output Format
-```
-30.0
-```
 ### Example Walkthrough
 In the sample, the price is 10 and the quantity is 3. The `Item` object's `total` method returns 10 x 3 = 30.0, so the program prints `30.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>modeling-with-classes</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O39" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P39" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>1</v>
+      </c>
+      <c r="R39" t="inlineStr">
         <is>
           <t>10
 3</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>30.0</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>5.5
 2</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>0
 10</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>100
 0</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>7.25
 4</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>29.0</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>-1
 5</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>-5.0</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>99.99
 1</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE39" t="inlineStr">
         <is>
           <t>99.99</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AG39" t="inlineStr">
         <is>
           <t>class Item:
- def __init__(self,p,q): self.price=p; self.qty=q
- def total(self): return self.price*self.qty
+ def __init__(self,p,q): self.price=p; self.qty=q   # both values stored as attributes on the object
+ def total(self): return self.price*self.qty   # self.price and self.qty belong to this object
 i=Item(float(input()),int(input())); print(i.total())</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Python - Temperature Class</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>A weather app models each reading as a `Temperature` object created from a Celsius value, with a `fahrenheit` method that converts and returns the equivalent Fahrenheit temperature for the app's international users.
 Define a `Temperature` class whose constructor takes a Celsius value `c`, with a `fahrenheit` method that returns `c * 9 / 5 + 32`. Read a Celsius value, create a `Temperature` object, and print the result of calling `fahrenheit` on it.
-### Input Format
-- Line 1: Temperature in Celsius
-### Output Format
-```
-32.0
-```
 ### Example Walkthrough
 In the sample, the Celsius value is 0. The `Temperature` object's `fahrenheit` method returns 0 x 9 / 5 + 32 = 32.0, so the program prints `32.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>attributes-and-methods</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O40" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P40" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="b">
+        <v>1</v>
+      </c>
+      <c r="R40" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>32.0</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>98.6</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>212.0</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>-40</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>-40.0</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>77.0</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE40" t="inlineStr">
         <is>
           <t>30.2</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG40" t="inlineStr">
         <is>
           <t>class Temperature:
- def __init__(self,c): self.c=c
- def fahrenheit(self): return self.c*9/5+32
+ def __init__(self,c): self.c=c   # constructor stores the Celsius value on the object
+ def fahrenheit(self): return self.c*9/5+32   # self.c is this object's own stored value
 t=Temperature(float(input())); print(t.fahrenheit())</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Python - Student Average Class</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>A report-card app models a student as a `Student` object holding a list of test marks, with an `average` method that returns the student's overall average score for the term.
 Define a `Student` class whose constructor takes a list of marks, with an `average` method that returns the sum of the marks divided by how many there are. Read a line of space-separated whole numbers, create a `Student` object with them, and print the result of calling `average` on it.
-### Input Format
-- Line 1: Space-separated marks
-### Output Format
-```
-85.0
-```
 ### Example Walkthrough
 In the sample, the marks are `80 90`. The `Student` object's `average` method returns (80 + 90) / 2 = 85.0, so the program prints `85.0`.
 ### Constraints
 - All numeric inputs are valid whole numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>object-oriented-programming-intro</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>modeling-with-classes</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O41" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P41" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="b">
+        <v>1</v>
+      </c>
+      <c r="R41" t="inlineStr">
         <is>
           <t>80 90</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>85.0</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>0 50 100</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>10 20 30</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>5 5 5</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>-10 10</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>99 100 98</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE41" t="inlineStr">
         <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG41" t="inlineStr">
         <is>
           <t>class Student:
- def __init__(self,m): self.marks=m
- def average(self): return sum(self.marks)/len(self.marks)
+ def __init__(self,m): self.marks=m   # constructor stores the marks list as an attribute
+ def average(self): return sum(self.marks)/len(self.marks)   # self.marks belongs to this object
 s=Student(list(map(int,input().split()))); print(s.average())</t>
         </is>
       </c>
